--- a/1. Database Desgin/Java23 CongHoang Database Design.xlsx
+++ b/1. Database Desgin/Java23 CongHoang Database Design.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java23\3. Database\1. Database Desgin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6264BC90-79C5-4BF1-A9CE-4E23537F006C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A3D3B4-3BC7-48E2-805E-2E029C5B2142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="588" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="588" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mô hình quan niệm" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="RD - Mô hình quan hệ" sheetId="3" r:id="rId3"/>
     <sheet name="B3. Mô hình quan hệ" sheetId="5" r:id="rId4"/>
     <sheet name="DB - Mô hình vật lý" sheetId="4" r:id="rId5"/>
+    <sheet name="B5. Tạo dữ liệu mẫu" sheetId="7" r:id="rId6"/>
+    <sheet name="Tạo dữ liệu mẫu" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -89,6 +91,7 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>HOANG</author>
     <author>tc={4CD9D1DD-78B3-4F1E-AABF-5374536358D4}</author>
     <author>tc={1817A709-4DC5-4C33-84B9-07B7BE8011EF}</author>
     <author>tc={07AD6B59-1590-4401-853F-A7409D722727}</author>
@@ -97,7 +100,32 @@
     <author>tc={A9C7C1FB-C102-4D11-B145-9F77A105ED1A}</author>
   </authors>
   <commentList>
-    <comment ref="K6" authorId="0" shapeId="0" xr:uid="{4CD9D1DD-78B3-4F1E-AABF-5374536358D4}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{D7FA8516-90DB-4863-A1F8-94768E483A70}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>HOANG:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Khi có thêm color, sẽ có thêm tính năng chọn màu sắc để hiển thị hình ảnh
+Không có color, show danh sách các hình ảnh</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K6" authorId="1" shapeId="0" xr:uid="{4CD9D1DD-78B3-4F1E-AABF-5374536358D4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -108,7 +136,7 @@
 Giám Đốc</t>
       </text>
     </comment>
-    <comment ref="L6" authorId="1" shapeId="0" xr:uid="{1817A709-4DC5-4C33-84B9-07B7BE8011EF}">
+    <comment ref="L6" authorId="2" shapeId="0" xr:uid="{1817A709-4DC5-4C33-84B9-07B7BE8011EF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -122,7 +150,7 @@
 Hủy đơn hàng</t>
       </text>
     </comment>
-    <comment ref="N6" authorId="2" shapeId="0" xr:uid="{07AD6B59-1590-4401-853F-A7409D722727}">
+    <comment ref="N6" authorId="3" shapeId="0" xr:uid="{07AD6B59-1590-4401-853F-A7409D722727}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -133,7 +161,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="Q7" authorId="3" shapeId="0" xr:uid="{E98505CF-4978-4366-B398-E9D46B405FAA}">
+    <comment ref="Q7" authorId="4" shapeId="0" xr:uid="{E98505CF-4978-4366-B398-E9D46B405FAA}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -141,7 +169,7 @@
     Số lượng bán của mặt hàng trong đơn hàng</t>
       </text>
     </comment>
-    <comment ref="D10" authorId="4" shapeId="0" xr:uid="{66C6B479-A7A9-4A4D-97F0-0671BA10393D}">
+    <comment ref="D10" authorId="5" shapeId="0" xr:uid="{66C6B479-A7A9-4A4D-97F0-0671BA10393D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -149,7 +177,7 @@
     Số lượng tồn kho theo mặt hàng, kích cỡ</t>
       </text>
     </comment>
-    <comment ref="G12" authorId="5" shapeId="0" xr:uid="{A9C7C1FB-C102-4D11-B145-9F77A105ED1A}">
+    <comment ref="G12" authorId="6" shapeId="0" xr:uid="{A9C7C1FB-C102-4D11-B145-9F77A105ED1A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -161,8 +189,233 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={D47D4195-AC10-4563-9960-DA4A0C01CCA2}</author>
+    <author>tc={B47EEB5D-31E3-4836-90FA-454834CBD42E}</author>
+    <author>tc={F40892D4-E542-45B8-AEEF-C34C4E7DFFE2}</author>
+    <author>tc={D27A5F0C-2010-47B9-A719-92C830BF60DB}</author>
+    <author>tc={D016D15D-534D-4D1E-BC05-4FEC27A667C8}</author>
+  </authors>
+  <commentList>
+    <comment ref="J26" authorId="0" shapeId="0" xr:uid="{D47D4195-AC10-4563-9960-DA4A0C01CCA2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="1" shapeId="0" xr:uid="{B47EEB5D-31E3-4836-90FA-454834CBD42E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Số lượng hàng còn lại ở thời điểm hiện tại</t>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="2" shapeId="0" xr:uid="{F40892D4-E542-45B8-AEEF-C34C4E7DFFE2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Khách
+Nhân Viên
+Quản Lý 
+Giám Đốc</t>
+      </text>
+    </comment>
+    <comment ref="C83" authorId="3" shapeId="0" xr:uid="{D27A5F0C-2010-47B9-A719-92C830BF60DB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tiền mặt, thẻ tín dụng, thẻ ghi nợ, ví điện tử</t>
+      </text>
+    </comment>
+    <comment ref="I90" authorId="4" shapeId="0" xr:uid="{D016D15D-534D-4D1E-BC05-4FEC27A667C8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Người tạo</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={22DF1135-398B-41D6-92DF-8FA9AC41F648}</author>
+    <author>tc={394ABE11-3D4F-48FF-B1E5-3A2103AE2E52}</author>
+    <author>tc={4D857E72-16E1-4D71-A318-2A677C582A9D}</author>
+    <author>tc={6606900E-86C1-4412-ABA5-C1A81BF963B0}</author>
+    <author>tc={E654F29F-BA1F-4923-B693-4724639E90B3}</author>
+    <author>Quyen Ngoc Phan</author>
+    <author>tc={C6165482-4873-4A9B-94D3-1061FF7CD07B}</author>
+    <author>tc={3C426FA6-F24A-4FAD-9E1A-FE681537D941}</author>
+    <author>tc={43CE2577-D5AF-47AD-984B-531EB84EA51E}</author>
+    <author>tc={DDFEA751-386D-44A8-AD15-117570C58F1B}</author>
+  </authors>
+  <commentList>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{22DF1135-398B-41D6-92DF-8FA9AC41F648}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Các sản phầm mua vào đều chung giá, k quan tâm kích cỡ, màu sắc, chất liệu</t>
+      </text>
+    </comment>
+    <comment ref="K5" authorId="1" shapeId="0" xr:uid="{394ABE11-3D4F-48FF-B1E5-3A2103AE2E52}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Chờ xác nhận, Đang đóng gói, Đóng gói hoàn thành chờ vận chuyển, Đang vận chuyển, Giao hàng thành công, Giao hàng thất bại, Hủy đơn hàng</t>
+      </text>
+    </comment>
+    <comment ref="H15" authorId="2" shapeId="0" xr:uid="{4D857E72-16E1-4D71-A318-2A677C582A9D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tiền mặt, thẻ tín dụng, thẻ ghi nợ, ví điện tử</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="3" shapeId="0" xr:uid="{6606900E-86C1-4412-ABA5-C1A81BF963B0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Không cần thuộc phòng ban, làm được mọi chức năng</t>
+      </text>
+    </comment>
+    <comment ref="I57" authorId="4" shapeId="0" xr:uid="{E654F29F-BA1F-4923-B693-4724639E90B3}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    NhanVien, Quan Ly</t>
+      </text>
+    </comment>
+    <comment ref="C71" authorId="5" shapeId="0" xr:uid="{8458CDB8-9993-4410-A2D2-AC429AF41744}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Lưu KDL DATE
+VD: 25/03 --&gt; tương ứng với ngày 25/03 0H0</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D71" authorId="5" shapeId="0" xr:uid="{CAB999B2-A63B-40FC-8E6B-82BDE15CF24A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Lưu KDL DATE
+VD: 28/03 --&gt; tương ứng với ngày 28/3 23H59H59
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E71" authorId="6" shapeId="0" xr:uid="{C6165482-4873-4A9B-94D3-1061FF7CD07B}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Số lượng bán
+</t>
+      </text>
+    </comment>
+    <comment ref="F71" authorId="7" shapeId="0" xr:uid="{3C426FA6-F24A-4FAD-9E1A-FE681537D941}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Doanh thu cho mặt hàng theo giai đoạn</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="5" shapeId="0" xr:uid="{D4C99250-9CAE-4B47-89E0-9111EF35646F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quyen Ngoc Phan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Bảng doanh thu, lưu doanh thu bán hàng từ ngày from đến ngày until số tiền bao nhiêu
+Chưa xử lý lưu trữ danh sách mặt hàng, đơn hàng</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E84" authorId="8" shapeId="0" xr:uid="{43CE2577-D5AF-47AD-984B-531EB84EA51E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</t>
+      </text>
+    </comment>
+    <comment ref="G84" authorId="9" shapeId="0" xr:uid="{DDFEA751-386D-44A8-AD15-117570C58F1B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Số lượng hàng còn lại ở thời điểm hiện tại</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="759">
   <si>
     <t>MatHang</t>
   </si>
@@ -1235,21 +1488,12 @@
     <t>C07_CUSTOMER_DOB</t>
   </si>
   <si>
-    <t>T09_ACCOUNT</t>
-  </si>
-  <si>
     <t>C07_CUSTOMER_ID</t>
   </si>
   <si>
     <t>C07_CUSTOMER_ADDRESS</t>
   </si>
   <si>
-    <t>C09_USERNAME</t>
-  </si>
-  <si>
-    <t>C09_PASSWORD</t>
-  </si>
-  <si>
     <t>T10_ROLE</t>
   </si>
   <si>
@@ -1259,12 +1503,6 @@
     <t>C10_ROLE_NAME</t>
   </si>
   <si>
-    <t>C09_ROLE_ID</t>
-  </si>
-  <si>
-    <t>C07_ACCOUNT_ID</t>
-  </si>
-  <si>
     <t>T11_ORDER_STATUS</t>
   </si>
   <si>
@@ -1301,9 +1539,6 @@
     <t>C06_PAYMENT_METHOD_ID</t>
   </si>
   <si>
-    <t>C06_EMPLOYEE_ID</t>
-  </si>
-  <si>
     <t>T08_EMPLOYEE</t>
   </si>
   <si>
@@ -1328,12 +1563,6 @@
     <t>C08_TITLE_ID</t>
   </si>
   <si>
-    <t>C08_ACCOUNT_ID</t>
-  </si>
-  <si>
-    <t>T14_TITLE</t>
-  </si>
-  <si>
     <t>T15_BILL</t>
   </si>
   <si>
@@ -1343,12 +1572,6 @@
     <t>C15_DELIVERY_FEE</t>
   </si>
   <si>
-    <t>C14_TITLE_ID</t>
-  </si>
-  <si>
-    <t>C14_TITLE_NAME</t>
-  </si>
-  <si>
     <t>C15_TOTAL_OF_MONEY</t>
   </si>
   <si>
@@ -1421,9 +1644,6 @@
     <t>C04_ITEM_GROUP_ID</t>
   </si>
   <si>
-    <t>C09_ACCOUNT_ID</t>
-  </si>
-  <si>
     <t>C17_IRN_ID</t>
   </si>
   <si>
@@ -1437,9 +1657,6 @@
   </si>
   <si>
     <t>C07_CUSTOMER_EMAIL</t>
-  </si>
-  <si>
-    <t>C09_ACCOUNT_STATUS</t>
   </si>
   <si>
     <t>Khóa chính này có 2 columns, được tham chiếu từ table khác</t>
@@ -1680,12 +1897,987 @@
   <si>
     <t>- Lưu ý: Dữ liệu trong cột khóa ngoại có thể trùng nhau để đảm bảo mối liên kết 1-n</t>
   </si>
+  <si>
+    <t>C01_BUY_PRICE</t>
+  </si>
+  <si>
+    <t>T02_ITEMGROUP</t>
+  </si>
+  <si>
+    <t>T05_ORDER_STATUS</t>
+  </si>
+  <si>
+    <t>T08_TITLE</t>
+  </si>
+  <si>
+    <t>Áo 1</t>
+  </si>
+  <si>
+    <t>C02_ITEMGROUP_ID</t>
+  </si>
+  <si>
+    <t>C02_ITEMGROUP_NAME</t>
+  </si>
+  <si>
+    <t>C05_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C05_ORDER_STATUS_DESC</t>
+  </si>
+  <si>
+    <t>C08_TITLE_NAME</t>
+  </si>
+  <si>
+    <t>Áo 2</t>
+  </si>
+  <si>
+    <t>Áo</t>
+  </si>
+  <si>
+    <t>Chờ xác nhận</t>
+  </si>
+  <si>
+    <t>Nhân viên</t>
+  </si>
+  <si>
+    <t>Áo 3</t>
+  </si>
+  <si>
+    <t>Quần</t>
+  </si>
+  <si>
+    <t>Trưởng bộ phận</t>
+  </si>
+  <si>
+    <t>Quần 4</t>
+  </si>
+  <si>
+    <t>Giày</t>
+  </si>
+  <si>
+    <t>Đóng gói hoàn thành</t>
+  </si>
+  <si>
+    <t>Giám đốc</t>
+  </si>
+  <si>
+    <t>Quần 5</t>
+  </si>
+  <si>
+    <t>Dép</t>
+  </si>
+  <si>
+    <t>Đang vận chuyển</t>
+  </si>
+  <si>
+    <t>Chủ sở hữu</t>
+  </si>
+  <si>
+    <t>Giày 6</t>
+  </si>
+  <si>
+    <t>Mũ</t>
+  </si>
+  <si>
+    <t>Giao hàng thành công</t>
+  </si>
+  <si>
+    <t>Giày 7</t>
+  </si>
+  <si>
+    <t>Thắt lưng</t>
+  </si>
+  <si>
+    <t>Giao hàng thất bại</t>
+  </si>
+  <si>
+    <t>Giày 8</t>
+  </si>
+  <si>
+    <t>Túi xách</t>
+  </si>
+  <si>
+    <t>Hủy đơn hàng</t>
+  </si>
+  <si>
+    <t>Giày 9</t>
+  </si>
+  <si>
+    <t>Giày 10</t>
+  </si>
+  <si>
+    <t>T04_PAYMENT_METHOD</t>
+  </si>
+  <si>
+    <t>T06_SIZE</t>
+  </si>
+  <si>
+    <t>Giép 11</t>
+  </si>
+  <si>
+    <t>C04_PMETHOD_ID</t>
+  </si>
+  <si>
+    <t>C04_PMETHOD_DESC</t>
+  </si>
+  <si>
+    <t>C06_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C06_SIZE_NAME</t>
+  </si>
+  <si>
+    <t>C06_GENDER</t>
+  </si>
+  <si>
+    <t>C06_SIZE_DESC</t>
+  </si>
+  <si>
+    <t>Áo 12</t>
+  </si>
+  <si>
+    <t>Tiền mặt</t>
+  </si>
+  <si>
+    <t>Size 'S' cho Nữ</t>
+  </si>
+  <si>
+    <t>Giép 13</t>
+  </si>
+  <si>
+    <t>Thẻ tín dụng</t>
+  </si>
+  <si>
+    <t>Size 'M' cho Nữ</t>
+  </si>
+  <si>
+    <t>Mũ 14</t>
+  </si>
+  <si>
+    <t>Thẻ ghi nợ</t>
+  </si>
+  <si>
+    <t>Size 'L' cho Nữ</t>
+  </si>
+  <si>
+    <t>Mũ 15</t>
+  </si>
+  <si>
+    <t>Ví điện tử</t>
+  </si>
+  <si>
+    <t>Size 'XL' cho Nữ</t>
+  </si>
+  <si>
+    <t>Thắt lưng 16</t>
+  </si>
+  <si>
+    <t>Size 'XXL' cho Nữ</t>
+  </si>
+  <si>
+    <t>Thắt lưng 17</t>
+  </si>
+  <si>
+    <t>Size 'S' cho Nam</t>
+  </si>
+  <si>
+    <t>Mũ 18</t>
+  </si>
+  <si>
+    <t>Size 'M' cho Nam</t>
+  </si>
+  <si>
+    <t>Túi xách 1</t>
+  </si>
+  <si>
+    <t>Size 'L' cho Nam</t>
+  </si>
+  <si>
+    <t>Túi xách 2</t>
+  </si>
+  <si>
+    <t>Size 'XL' cho Nam</t>
+  </si>
+  <si>
+    <t>Size 'XXL' cho Nam</t>
+  </si>
+  <si>
+    <t>T03_ORDER</t>
+  </si>
+  <si>
+    <t>Dùng công thức để tính</t>
+  </si>
+  <si>
+    <t>C03_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C03_ORDER_TIME</t>
+  </si>
+  <si>
+    <t>C03_DELIVERY_FEE</t>
+  </si>
+  <si>
+    <t>C03_DELIVERY_ADDRESS</t>
+  </si>
+  <si>
+    <t>C03_RECEIVER_PHONE</t>
+  </si>
+  <si>
+    <t>C03_TOTAL_OF_MONEY</t>
+  </si>
+  <si>
+    <t>C03_PMETHOD_ID</t>
+  </si>
+  <si>
+    <t>C03_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>10.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 1</t>
+  </si>
+  <si>
+    <t>12.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 2</t>
+  </si>
+  <si>
+    <t>14.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 3</t>
+  </si>
+  <si>
+    <t>16.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 4</t>
+  </si>
+  <si>
+    <t>18.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 5</t>
+  </si>
+  <si>
+    <t>Địa chỉ 6</t>
+  </si>
+  <si>
+    <t>Địa chỉ 7</t>
+  </si>
+  <si>
+    <t>Địa chỉ 8</t>
+  </si>
+  <si>
+    <t>Địa chỉ 9</t>
+  </si>
+  <si>
+    <t>Địa chỉ 10</t>
+  </si>
+  <si>
+    <t>20.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 11</t>
+  </si>
+  <si>
+    <t>26.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 12</t>
+  </si>
+  <si>
+    <t>28.04.2024 08:10:20</t>
+  </si>
+  <si>
+    <t>Địa chỉ 13</t>
+  </si>
+  <si>
+    <t>T11_CUSTOMER</t>
+  </si>
+  <si>
+    <t>C11_CUSTOMER_ID</t>
+  </si>
+  <si>
+    <t>C11_CUSTOMER_NAME</t>
+  </si>
+  <si>
+    <t>C11_CUSTOMER_EMAIL</t>
+  </si>
+  <si>
+    <t>C11_CUSTOMER_ADDRESS</t>
+  </si>
+  <si>
+    <t>C11_CUSTOMER_PHONE</t>
+  </si>
+  <si>
+    <t>C11_CUSTOMER_USERNAME</t>
+  </si>
+  <si>
+    <t>C11_CUSTOMER_PASSWORD</t>
+  </si>
+  <si>
+    <t>Lê Tèo</t>
+  </si>
+  <si>
+    <t>c1@gmal.com</t>
+  </si>
+  <si>
+    <t>c1def</t>
+  </si>
+  <si>
+    <t>$2a$12$w0bs0MW/O3nTyMhuv0r1jOjq2gOaxLxkZgms7u/khHRmtCh3S/Hpu</t>
+  </si>
+  <si>
+    <t>Văn An</t>
+  </si>
+  <si>
+    <t>c2@gmal.com</t>
+  </si>
+  <si>
+    <t>c2auto</t>
+  </si>
+  <si>
+    <t>Nguyễn A</t>
+  </si>
+  <si>
+    <t>c3@gmal.com</t>
+  </si>
+  <si>
+    <t>c3def</t>
+  </si>
+  <si>
+    <t>Phan Tuấn</t>
+  </si>
+  <si>
+    <t>c4@gmal.com</t>
+  </si>
+  <si>
+    <t>c4auto</t>
+  </si>
+  <si>
+    <t>Hoàng Tiên</t>
+  </si>
+  <si>
+    <t>c5@gmal.com</t>
+  </si>
+  <si>
+    <t>c5def</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc</t>
+  </si>
+  <si>
+    <t>c6@gmal.com</t>
+  </si>
+  <si>
+    <t>c6auto</t>
+  </si>
+  <si>
+    <t>Đoạn Tú</t>
+  </si>
+  <si>
+    <t>c7@gmal.com</t>
+  </si>
+  <si>
+    <t>c7def</t>
+  </si>
+  <si>
+    <t>Hoàng B</t>
+  </si>
+  <si>
+    <t>c8@gmal.com</t>
+  </si>
+  <si>
+    <t>c8auto</t>
+  </si>
+  <si>
+    <t>Lê Huân</t>
+  </si>
+  <si>
+    <t>c9@gmal.com</t>
+  </si>
+  <si>
+    <t>c9def</t>
+  </si>
+  <si>
+    <t>Nam Ban</t>
+  </si>
+  <si>
+    <t>c10@gmal.com</t>
+  </si>
+  <si>
+    <t>c10auto</t>
+  </si>
+  <si>
+    <t>T07_EMPLOYEE</t>
+  </si>
+  <si>
+    <t>C07_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C07_EMPLOYEE_NAME</t>
+  </si>
+  <si>
+    <t>C07_EMPLOYEE_EMAIL</t>
+  </si>
+  <si>
+    <t>C07_EMPLOYEE_ADDRESS</t>
+  </si>
+  <si>
+    <t>C07_EMPLOYEE_PHONE</t>
+  </si>
+  <si>
+    <t>C07_EMPLOYEE_USERNAME</t>
+  </si>
+  <si>
+    <t>C07_EMPLOYEE_PASSWORD</t>
+  </si>
+  <si>
+    <t>C07_TITLE_ID</t>
+  </si>
+  <si>
+    <t>Nhân viên 1</t>
+  </si>
+  <si>
+    <t>nv1@gmal.com</t>
+  </si>
+  <si>
+    <t>nv1def</t>
+  </si>
+  <si>
+    <t>Nhân viên 2</t>
+  </si>
+  <si>
+    <t>nv2@gmal.com</t>
+  </si>
+  <si>
+    <t>nv2auto</t>
+  </si>
+  <si>
+    <t>Nhân viên 3</t>
+  </si>
+  <si>
+    <t>nv3@gmal.com</t>
+  </si>
+  <si>
+    <t>nv3def</t>
+  </si>
+  <si>
+    <t>Nhân viên 4</t>
+  </si>
+  <si>
+    <t>nv4@gmal.com</t>
+  </si>
+  <si>
+    <t>nv4auto</t>
+  </si>
+  <si>
+    <t>Nhân viên 5</t>
+  </si>
+  <si>
+    <t>nv5@gmail.com</t>
+  </si>
+  <si>
+    <t>nv5def</t>
+  </si>
+  <si>
+    <t>Nhân viên 6</t>
+  </si>
+  <si>
+    <t>nv6@gmal.com</t>
+  </si>
+  <si>
+    <t>nv6auto</t>
+  </si>
+  <si>
+    <t>Nhân viên 7</t>
+  </si>
+  <si>
+    <t>nv7@gmal.com</t>
+  </si>
+  <si>
+    <t>nv7def</t>
+  </si>
+  <si>
+    <t>Nhân viên 8</t>
+  </si>
+  <si>
+    <t>nv8@gmal.com</t>
+  </si>
+  <si>
+    <t>nv8auto</t>
+  </si>
+  <si>
+    <t>Nhân viên 9</t>
+  </si>
+  <si>
+    <t>nv9@gmal.com</t>
+  </si>
+  <si>
+    <t>nv9def</t>
+  </si>
+  <si>
+    <t>Nhân viên 10</t>
+  </si>
+  <si>
+    <t>nv10@gmal.com</t>
+  </si>
+  <si>
+    <t>nv10auto</t>
+  </si>
+  <si>
+    <t>T09_ITEM_STATISTIC</t>
+  </si>
+  <si>
+    <t>C09_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C09_DATE_FROM</t>
+  </si>
+  <si>
+    <t>C09_DATE_UNTIL</t>
+  </si>
+  <si>
+    <t>C09_SALES_AMOUNT</t>
+  </si>
+  <si>
+    <t>C09_REVENUE</t>
+  </si>
+  <si>
+    <t>Bài tập phần DML - Tạo câu truy vấn để xử lý</t>
+  </si>
+  <si>
+    <t>T10_REVENUE</t>
+  </si>
+  <si>
+    <t>C10_RID</t>
+  </si>
+  <si>
+    <t>C10_DATE_FROM</t>
+  </si>
+  <si>
+    <t>C10_DATE_UNITIL</t>
+  </si>
+  <si>
+    <t>C10_TOTAL_OF_MONEY</t>
+  </si>
+  <si>
+    <t>T12_ITEM_DETAIL</t>
+  </si>
+  <si>
+    <t>C12_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C12_ITEM_ID</t>
+  </si>
+  <si>
+    <t>C12_SIZE_ID</t>
+  </si>
+  <si>
+    <t>C12_COLOR</t>
+  </si>
+  <si>
+    <t>C12_SALES_PRICE</t>
+  </si>
+  <si>
+    <t>C12_AMOUNT</t>
+  </si>
+  <si>
+    <t>Fake 100 rows</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng ITEM, SIZE
+---
+ITEM, SIZE có ID lẻ: AMOUNT = 125, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5
+ITEM, SIZE có ID chẵn: AMOUNT = 280, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5 + 20</t>
+  </si>
+  <si>
+    <t>T13_GALLERY</t>
+  </si>
+  <si>
+    <t>C13_PATH</t>
+  </si>
+  <si>
+    <t>C13_ITEM_ID</t>
+  </si>
+  <si>
+    <t>Sử dụng ITEM ID từ bảng ITEM và fake default path</t>
+  </si>
+  <si>
+    <t>T14_ORDER_DETAIL</t>
+  </si>
+  <si>
+    <t>C14_ORDER_ID</t>
+  </si>
+  <si>
+    <t>C14_ITEM_DETAIL_ID</t>
+  </si>
+  <si>
+    <t>C14_AMOUNT</t>
+  </si>
+  <si>
+    <t>T15_ORDER_STATUS_DETAIL</t>
+  </si>
+  <si>
+    <t>Large amount of data</t>
+  </si>
+  <si>
+    <t>C15_ORDER_STATUS_ID</t>
+  </si>
+  <si>
+    <t>C15_EMPLOYEE_ID</t>
+  </si>
+  <si>
+    <t>C15_LAST_UPDATED</t>
+  </si>
+  <si>
+    <t>-- 1. Đơn hàng từ 1 - 5 --&gt; Giao thành công (trạng thái từ 1 - 5)</t>
+  </si>
+  <si>
+    <t>SYSDATE - [max(STATUS_ID) - ORDER_STATUS_Id]</t>
+  </si>
+  <si>
+    <t>-- 2 Đơn hàng từ 6 - 8 --&gt; Đóng gói thành công (trạng thái từ 1 - 3)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 2</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>-- 3. Đơn hàng từ 9 - 10 --&gt; Đang giao hàng (trạng thái từ 1 - 4)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 3</t>
+  </si>
+  <si>
+    <t>-- 4. Đơn hàng từ 11 - 12 --&gt; Hủy đơn hàng (trạng thái 7)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 4</t>
+  </si>
+  <si>
+    <t>-- 4. Đơn hàng từ 13  --&gt; Giao hàng thất bại (trạng thái 1,2,3,4,6)</t>
+  </si>
+  <si>
+    <t>Nhân Viên 5</t>
+  </si>
+  <si>
+    <t>C01_REF_ITEM_ID</t>
+  </si>
+  <si>
+    <t>T04_ITEMGROUP</t>
+  </si>
+  <si>
+    <t>C04_ITEMGROUP_ID</t>
+  </si>
+  <si>
+    <t>C04_ITEMGROUP_NAME</t>
+  </si>
+  <si>
+    <t>C05_COLOR_ID</t>
+  </si>
+  <si>
+    <t>Sử dụng ITEM ID từ bảng ITEM và fake default path
+----
+Cặp dữ liệu: itemId, randomColor, file://image/p_itemId.png</t>
+  </si>
+  <si>
+    <t>Sử dụng dữ liệu từ các bảng ITEM, SIZE
+---
+ITEM, SIZE có ID lẻ: AMOUNT = 125, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5
+ITEM, SIZE có ID chẵn: AMOUNT = 280, SALES_PRICE = BUY_PRICE * 2 + SIZE_ID * 5 + 20
+---
+1 item có thể có nhiều BUY_PRICE
+chọn BUY_PRICE của phiếu mới nhất hoặc BUY_PRICE có giá cao nhất trong tất cả các phiếu nhập</t>
+  </si>
+  <si>
+    <t>Nếu có ROLE và TITLE thì sẽ khác nhau gì</t>
+  </si>
+  <si>
+    <t>ROLE: Khách, Nhân Viên, Quản Lý, Giám Đốc =&gt; tác động đến permission của nhân viên và khách hàng khi vào ứng dụng</t>
+  </si>
+  <si>
+    <t>TITLE: Nhân viên giữ xe, nhân viên giao hàng, nhân viên bán hàng, nhân viên chạy quảng cáo =&gt; chọn nhân viên, quản lý làm công việc phù hợp</t>
+  </si>
+  <si>
+    <t>Nhân viên giữ xe</t>
+  </si>
+  <si>
+    <t>Nhân viên giao hàng</t>
+  </si>
+  <si>
+    <t>Nhân viên bán hàng</t>
+  </si>
+  <si>
+    <t>Nhân viên chạy quảng cáo</t>
+  </si>
+  <si>
+    <t>Quản lý 1</t>
+  </si>
+  <si>
+    <t>Quản lý 2</t>
+  </si>
+  <si>
+    <t>Quản lý</t>
+  </si>
+  <si>
+    <t>C07_USERNAME</t>
+  </si>
+  <si>
+    <t>C07_PASSWORD</t>
+  </si>
+  <si>
+    <t>C07_ACCOUNT_STATUS</t>
+  </si>
+  <si>
+    <t>Khách Hàng 1</t>
+  </si>
+  <si>
+    <t>$2a$12$VIV/HG44mCN3467Y.aEwoe6iTHNrIvr27keSCmZrVN4V7empgW/t.</t>
+  </si>
+  <si>
+    <t>Khách Hàng 2</t>
+  </si>
+  <si>
+    <t>sysdate</t>
+  </si>
+  <si>
+    <t>Khách Hàng 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - customerId(year)</t>
+  </si>
+  <si>
+    <t>Khách Hàng 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - customerId(day)</t>
+  </si>
+  <si>
+    <t>Khách Hàng 5</t>
+  </si>
+  <si>
+    <t>random</t>
+  </si>
+  <si>
+    <t>Khách Hàng 6</t>
+  </si>
+  <si>
+    <t>Khách Hàng 7</t>
+  </si>
+  <si>
+    <t>Khách Hàng 8</t>
+  </si>
+  <si>
+    <t>Khách Hàng 9</t>
+  </si>
+  <si>
+    <t>Khách Hàng 10</t>
+  </si>
+  <si>
+    <t>C08_USERNAME</t>
+  </si>
+  <si>
+    <t>C08_PASSWORD</t>
+  </si>
+  <si>
+    <t>C08_ACCOUNT_STATUS</t>
+  </si>
+  <si>
+    <t>C08_ROLE</t>
+  </si>
+  <si>
+    <t>Nhân viên 11</t>
+  </si>
+  <si>
+    <t>nv11auto</t>
+  </si>
+  <si>
+    <t>Nhân viên 12</t>
+  </si>
+  <si>
+    <t>nv12def</t>
+  </si>
+  <si>
+    <t>Nhân viên 13</t>
+  </si>
+  <si>
+    <t>nv13auto</t>
+  </si>
+  <si>
+    <t>C13_PMETHOD_ID</t>
+  </si>
+  <si>
+    <t>C13_PMETHOD_DESC</t>
+  </si>
+  <si>
+    <t>C06_CREATED_BY</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>Hủy Đơn Hàng</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>Duyệt danh sách ORDER có orderId
+----
++ billId: Tự động tăng
++ deliveryFee: random [20, 28, 48, 56, 80]
++ totalOfMoney: dựa vào order, item, order detail để tính tiền</t>
+  </si>
+  <si>
+    <t>today -  irn_id</t>
+  </si>
+  <si>
+    <t>6 8 9</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A1</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A2</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A3</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A4</t>
+  </si>
+  <si>
+    <t>Nhà cung cấp A5</t>
+  </si>
+  <si>
+    <t>ITEM_ID || ITEM_ID - 10</t>
+  </si>
+  <si>
+    <t>Lấy từ T01_ITEM</t>
+  </si>
+  <si>
+    <t>random 200 400 580 600 1200</t>
+  </si>
+  <si>
+    <t>random 88 122 244 366 150</t>
+  </si>
+  <si>
+    <t>random 1 2 3 4 5</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>c1@gmail.com</t>
+  </si>
+  <si>
+    <t>c2@gmail.com</t>
+  </si>
+  <si>
+    <t>c3@gmail.com</t>
+  </si>
+  <si>
+    <t>c4@gmail.com</t>
+  </si>
+  <si>
+    <t>c5@gmail.com</t>
+  </si>
+  <si>
+    <t>c6@gmail.com</t>
+  </si>
+  <si>
+    <t>c7@gmail.com</t>
+  </si>
+  <si>
+    <t>c8@gmail.com</t>
+  </si>
+  <si>
+    <t>c9@gmail.com</t>
+  </si>
+  <si>
+    <t>c10@gmail.com</t>
+  </si>
+  <si>
+    <t>nv1@gmail.com</t>
+  </si>
+  <si>
+    <t>nv2@gmail.com</t>
+  </si>
+  <si>
+    <t>nv3@gmail.com</t>
+  </si>
+  <si>
+    <t>nv4@gmail.com</t>
+  </si>
+  <si>
+    <t>nv6@gmail.com</t>
+  </si>
+  <si>
+    <t>nv7@gmail.com</t>
+  </si>
+  <si>
+    <t>nv8@gmail.com</t>
+  </si>
+  <si>
+    <t>nv9@gmail.com</t>
+  </si>
+  <si>
+    <t>nv10@gmail.com</t>
+  </si>
+  <si>
+    <t>nv11@gmail.com</t>
+  </si>
+  <si>
+    <t>nv12@gmail.com</t>
+  </si>
+  <si>
+    <t>nv13@gmail.com</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1825,6 +3017,57 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -1900,7 +3143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1943,12 +3186,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2121,6 +3382,75 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2137,6 +3467,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2508,6 +3856,62 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J26" dT="2024-04-02T12:50:53.71" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{D47D4195-AC10-4563-9960-DA4A0C01CCA2}">
+    <text>Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</text>
+  </threadedComment>
+  <threadedComment ref="L26" dT="2024-04-02T13:53:18.17" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{B47EEB5D-31E3-4836-90FA-454834CBD42E}">
+    <text>Số lượng hàng còn lại ở thời điểm hiện tại</text>
+  </threadedComment>
+  <threadedComment ref="C40" dT="2025-03-02T14:20:09.75" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{F40892D4-E542-45B8-AEEF-C34C4E7DFFE2}">
+    <text>Khách
+Nhân Viên
+Quản Lý 
+Giám Đốc</text>
+  </threadedComment>
+  <threadedComment ref="C83" dT="2024-04-06T14:23:17.00" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{D27A5F0C-2010-47B9-A719-92C830BF60DB}">
+    <text>Tiền mặt, thẻ tín dụng, thẻ ghi nợ, ví điện tử</text>
+  </threadedComment>
+  <threadedComment ref="I90" dT="2025-03-02T14:36:28.94" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{D016D15D-534D-4D1E-BC05-4FEC27A667C8}">
+    <text>Người tạo</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D4" dT="2024-03-19T12:47:34.71" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{22DF1135-398B-41D6-92DF-8FA9AC41F648}">
+    <text>Các sản phầm mua vào đều chung giá, k quan tâm kích cỡ, màu sắc, chất liệu</text>
+  </threadedComment>
+  <threadedComment ref="K5" dT="2024-04-06T14:25:21.49" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{394ABE11-3D4F-48FF-B1E5-3A2103AE2E52}">
+    <text>Chờ xác nhận, Đang đóng gói, Đóng gói hoàn thành chờ vận chuyển, Đang vận chuyển, Giao hàng thành công, Giao hàng thất bại, Hủy đơn hàng</text>
+  </threadedComment>
+  <threadedComment ref="H15" dT="2024-04-06T14:23:17.00" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{4D857E72-16E1-4D71-A318-2A677C582A9D}">
+    <text>Tiền mặt, thẻ tín dụng, thẻ ghi nợ, ví điện tử</text>
+  </threadedComment>
+  <threadedComment ref="B56" dT="2024-03-19T13:48:38.72" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{6606900E-86C1-4412-ABA5-C1A81BF963B0}">
+    <text>Không cần thuộc phòng ban, làm được mọi chức năng</text>
+  </threadedComment>
+  <threadedComment ref="I57" dT="2024-03-19T13:49:56.69" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{E654F29F-BA1F-4923-B693-4724639E90B3}">
+    <text>NhanVien, Quan Ly</text>
+  </threadedComment>
+  <threadedComment ref="E71" dT="2024-04-02T13:49:52.63" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{C6165482-4873-4A9B-94D3-1061FF7CD07B}">
+    <text xml:space="preserve">Số lượng bán
+</text>
+  </threadedComment>
+  <threadedComment ref="F71" dT="2024-04-02T13:55:15.51" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{3C426FA6-F24A-4FAD-9E1A-FE681537D941}">
+    <text>Doanh thu cho mặt hàng theo giai đoạn</text>
+  </threadedComment>
+  <threadedComment ref="E84" dT="2024-04-02T12:50:53.71" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{43CE2577-D5AF-47AD-984B-531EB84EA51E}">
+    <text>Có rất nhiều màu sắc color, rgb, hexa -&gt; sử dụng varchar để lưu chứ k tạo 1 bảng riêng</text>
+  </threadedComment>
+  <threadedComment ref="G84" dT="2024-04-02T13:53:18.17" personId="{1555D0CD-EB71-4013-AD6F-446804E4114E}" id="{DDFEA751-386D-44A8-AD15-117570C58F1B}">
+    <text>Số lượng hàng còn lại ở thời điểm hiện tại</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:P28"/>
@@ -3250,12 +4654,12 @@
       <c r="Q13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="R13" s="68" t="s">
+      <c r="R13" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="S13" s="68"/>
-      <c r="T13" s="68"/>
-      <c r="U13" s="68"/>
+      <c r="S13" s="91"/>
+      <c r="T13" s="91"/>
+      <c r="U13" s="91"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
@@ -3268,10 +4672,10 @@
       <c r="Q14" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
+      <c r="R14" s="91"/>
+      <c r="S14" s="91"/>
+      <c r="T14" s="91"/>
+      <c r="U14" s="91"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
@@ -3846,10 +5250,10 @@
       <c r="W18" s="5"/>
     </row>
     <row r="19" spans="3:35" x14ac:dyDescent="0.25">
-      <c r="P19" s="73" t="s">
+      <c r="P19" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="Q19" s="73"/>
+      <c r="Q19" s="96"/>
       <c r="T19" s="4" t="s">
         <v>9</v>
       </c>
@@ -3867,10 +5271,10 @@
       <c r="P20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Q20" s="72" t="s">
+      <c r="Q20" s="95" t="s">
         <v>14</v>
       </c>
-      <c r="R20" s="72"/>
+      <c r="R20" s="95"/>
       <c r="T20" s="4" t="s">
         <v>94</v>
       </c>
@@ -3888,10 +5292,10 @@
       <c r="P21" s="4">
         <v>1</v>
       </c>
-      <c r="Q21" s="72" t="s">
+      <c r="Q21" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="R21" s="72"/>
+      <c r="R21" s="95"/>
       <c r="T21" s="4" t="s">
         <v>94</v>
       </c>
@@ -3909,10 +5313,10 @@
       <c r="P22" s="4">
         <v>2</v>
       </c>
-      <c r="Q22" s="72" t="s">
+      <c r="Q22" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="R22" s="72"/>
+      <c r="R22" s="95"/>
       <c r="T22" s="4" t="s">
         <v>94</v>
       </c>
@@ -3930,10 +5334,10 @@
       <c r="P23" s="4">
         <v>3</v>
       </c>
-      <c r="Q23" s="72" t="s">
+      <c r="Q23" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="R23" s="72"/>
+      <c r="R23" s="95"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
@@ -3952,10 +5356,10 @@
       <c r="P24" s="4">
         <v>4</v>
       </c>
-      <c r="Q24" s="72" t="s">
+      <c r="Q24" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="R24" s="72"/>
+      <c r="R24" s="95"/>
       <c r="T24" s="4" t="s">
         <v>95</v>
       </c>
@@ -4600,16 +6004,16 @@
       </c>
     </row>
     <row r="48" spans="3:36" x14ac:dyDescent="0.25">
-      <c r="C48" s="69" t="s">
+      <c r="C48" s="92" t="s">
         <v>216</v>
       </c>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="70"/>
+      <c r="D48" s="93"/>
+      <c r="E48" s="93"/>
+      <c r="F48" s="93"/>
+      <c r="G48" s="93"/>
+      <c r="H48" s="93"/>
+      <c r="I48" s="93"/>
+      <c r="J48" s="93"/>
       <c r="O48" s="25">
         <v>3</v>
       </c>
@@ -4639,16 +6043,16 @@
       </c>
     </row>
     <row r="49" spans="3:32" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="71" t="s">
+      <c r="C49" s="94" t="s">
         <v>215</v>
       </c>
-      <c r="D49" s="71"/>
-      <c r="E49" s="71"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="71"/>
-      <c r="H49" s="71"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="71"/>
+      <c r="D49" s="94"/>
+      <c r="E49" s="94"/>
+      <c r="F49" s="94"/>
+      <c r="G49" s="94"/>
+      <c r="H49" s="94"/>
+      <c r="I49" s="94"/>
+      <c r="J49" s="94"/>
       <c r="O49" s="25">
         <v>4</v>
       </c>
@@ -5123,48 +6527,48 @@
   <sheetData>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="F2" s="15" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5190,16 +6594,16 @@
         <v>13</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>246</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>256</v>
@@ -5231,7 +6635,7 @@
         <v>7</v>
       </c>
       <c r="H5" s="54" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="I5" s="54" t="s">
         <v>266</v>
@@ -5246,18 +6650,18 @@
         <v>251</v>
       </c>
       <c r="M5" s="54" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="N5" s="54" t="s">
         <v>268</v>
       </c>
       <c r="O5" s="54" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="51" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>228</v>
@@ -5266,19 +6670,19 @@
         <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="F6" s="54" t="s">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>248</v>
@@ -5290,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>269</v>
@@ -5301,7 +6705,7 @@
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>3</v>
@@ -5311,7 +6715,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
@@ -5333,14 +6737,14 @@
         <v>252</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B8" s="51" t="s">
         <v>225</v>
@@ -5373,7 +6777,7 @@
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="51" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -5399,7 +6803,7 @@
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="51" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="51" t="s">
@@ -5423,7 +6827,7 @@
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="51" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="51" t="s">
@@ -5432,7 +6836,7 @@
       <c r="E11" s="51"/>
       <c r="F11" s="2"/>
       <c r="G11" s="51" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="H11" s="51" t="s">
         <v>246</v>
@@ -5455,7 +6859,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="51" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="I12" s="51"/>
       <c r="J12" s="2"/>
@@ -5594,13 +6998,13 @@
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C23" s="66" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24" spans="2:17" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24" s="20" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -5618,17 +7022,17 @@
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C25" s="20" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C27" s="66" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C28" s="20" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="L28" s="45"/>
       <c r="M28" s="45"/>
@@ -5638,7 +7042,7 @@
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C29" s="20" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="L29" s="45"/>
       <c r="M29" s="45"/>
@@ -5655,27 +7059,27 @@
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C31" s="66" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C32" s="20" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C33" s="20" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C35" s="66" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C36" s="20" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
@@ -5683,13 +7087,13 @@
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C38" s="20" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="45"/>
       <c r="C39" s="67" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="D39" s="45"/>
       <c r="E39" s="45"/>
@@ -5817,17 +7221,19 @@
   <sheetData>
     <row r="2" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="D3" s="5" t="s">
-        <v>367</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
       <c r="R3" s="5" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5853,40 +7259,36 @@
         <v>304</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>309</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="J4" s="1"/>
       <c r="K4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="M4" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>341</v>
-      </c>
+      <c r="O4" s="1"/>
       <c r="P4" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5897,10 +7299,10 @@
         <v>283</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E5" s="53" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="F5" s="53" t="s">
         <v>294</v>
@@ -5909,43 +7311,39 @@
         <v>299</v>
       </c>
       <c r="H5" s="53" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I5" s="53" t="s">
-        <v>333</v>
-      </c>
-      <c r="J5" s="53" t="s">
-        <v>371</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="J5" s="53"/>
       <c r="K5" s="53" t="s">
+        <v>312</v>
+      </c>
+      <c r="L5" s="53" t="s">
         <v>315</v>
       </c>
-      <c r="L5" s="53" t="s">
-        <v>320</v>
-      </c>
       <c r="M5" s="53" t="s">
+        <v>318</v>
+      </c>
+      <c r="N5" s="53" t="s">
         <v>323</v>
       </c>
-      <c r="N5" s="53" t="s">
-        <v>328</v>
-      </c>
-      <c r="O5" s="53" t="s">
-        <v>345</v>
-      </c>
+      <c r="O5" s="53"/>
       <c r="P5" s="53" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="Q5" s="53" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="R5" s="53" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
       <c r="S5" s="53" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="T5" s="53" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -5959,7 +7357,7 @@
         <v>289</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="F6" s="53" t="s">
         <v>295</v>
@@ -5971,45 +7369,41 @@
         <v>306</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>312</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>321</v>
-      </c>
       <c r="M6" s="53" t="s">
+        <v>319</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="2"/>
+      <c r="P6" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q6" s="53" t="s">
+        <v>341</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="S6" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q6" s="53" t="s">
-        <v>351</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="S6" s="53" t="s">
-        <v>362</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="52" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="C7" s="55" t="s">
         <v>285</v>
@@ -6028,36 +7422,36 @@
         <v>305</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>313</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="14"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="N7" s="57"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="R7" s="52" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="2:20" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>661</v>
+      </c>
       <c r="C8" s="2" t="s">
         <v>286</v>
       </c>
@@ -6067,31 +7461,29 @@
       <c r="E8" s="14"/>
       <c r="F8" s="2"/>
       <c r="G8" s="25" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>377</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="N8" s="57"/>
       <c r="O8" s="2"/>
       <c r="P8" s="52" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="T8" s="2"/>
     </row>
@@ -6110,11 +7502,9 @@
         <v>307</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J9" s="52" t="s">
-        <v>317</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="J9" s="52"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -6124,7 +7514,7 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="52" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="T9" s="2"/>
     </row>
@@ -6143,7 +7533,7 @@
         <v>308</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -6164,13 +7554,13 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="51" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I11" s="52" t="s">
-        <v>339</v>
+        <v>310</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -6190,13 +7580,13 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="51" t="s">
-        <v>331</v>
-      </c>
-      <c r="H12" s="52" t="s">
-        <v>318</v>
-      </c>
-      <c r="I12" s="52" t="s">
-        <v>340</v>
+        <v>708</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>697</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -6216,8 +7606,12 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="14"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>698</v>
+      </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -6237,8 +7631,12 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="51"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>699</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -6379,22 +7777,22 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="I23" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
@@ -6408,11 +7806,11 @@
         <v>282</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="K25" s="5"/>
       <c r="N25" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
@@ -6446,20 +7844,20 @@
         <v>1</v>
       </c>
       <c r="G27" s="19" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="H27" s="19"/>
       <c r="I27" s="19">
         <v>1</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.25">
@@ -6470,7 +7868,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="19" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="H28" s="19"/>
       <c r="I28" s="19">
@@ -6485,7 +7883,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="20" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
@@ -6505,13 +7903,13 @@
         <v>293</v>
       </c>
       <c r="H30" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="I30" s="19">
         <v>4</v>
       </c>
       <c r="J30" s="19" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -6531,7 +7929,7 @@
         <v>5</v>
       </c>
       <c r="J31" s="19" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -6542,27 +7940,27 @@
         <v>1</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="H32" s="58" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="I32" s="19">
         <v>6</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="59" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C33" s="60"/>
       <c r="D33" s="60"/>
@@ -6571,10 +7969,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="H33" s="58" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="I33" s="19">
         <v>7</v>
@@ -6588,25 +7986,25 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="59" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C34" s="59" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D34" s="59" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E34" s="59" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F34" s="19">
         <v>1</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="H34" s="58" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="I34" s="19">
         <v>8</v>
@@ -6623,28 +8021,28 @@
         <v>1</v>
       </c>
       <c r="C35" s="61" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="D35" s="61" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="E35" s="62" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="F35" s="19">
         <v>2</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="H35" s="58" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="I35" s="19">
         <v>9</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -6658,16 +8056,16 @@
         <v>100</v>
       </c>
       <c r="D36" s="61" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="E36" s="62" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="I36" s="19">
         <v>10</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -6678,15 +8076,15 @@
         <v>1</v>
       </c>
       <c r="C37" s="61" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="D37" s="61" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="E37" s="61"/>
       <c r="H37" s="19"/>
       <c r="J37" s="63" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="K37" s="31">
         <v>1</v>
@@ -6697,16 +8095,16 @@
         <v>2</v>
       </c>
       <c r="C38" s="61" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="D38" s="61" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="E38" s="62" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
@@ -6717,10 +8115,10 @@
         <v>100</v>
       </c>
       <c r="D39" s="61" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="E39" s="62" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="F39" s="19" t="s">
         <v>289</v>
@@ -6743,10 +8141,10 @@
         <v>2</v>
       </c>
       <c r="C40" s="61" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="D40" s="61" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E40" s="61"/>
       <c r="F40" s="19">
@@ -6756,7 +8154,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="I40" s="19">
         <v>220</v>
@@ -6770,10 +8168,10 @@
         <v>2</v>
       </c>
       <c r="C41" s="61" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="D41" s="61" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E41" s="61"/>
       <c r="F41" s="19">
@@ -6783,7 +8181,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="I41" s="19">
         <v>230</v>
@@ -6886,45 +8284,48 @@
     </row>
     <row r="49" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E49" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="50" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E50" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E51" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
     </row>
     <row r="53" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E53" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E54" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
     </row>
     <row r="56" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E56" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E57" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="58" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E58" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J3:K3"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="H32" r:id="rId1" xr:uid="{B5ECA51A-4D16-45CB-BA23-AC0AD8166D61}"/>
     <hyperlink ref="H33" r:id="rId2" display="file://img01" xr:uid="{6D09BE9B-5128-45C8-9E1D-DD81531512EF}"/>
@@ -6936,4 +8337,6323 @@
   <drawing r:id="rId6"/>
   <legacyDrawing r:id="rId7"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6331D375-C081-43D0-B98D-25BC6612D2D8}">
+  <dimension ref="A3:L201"/>
+  <sheetFormatPr defaultColWidth="30.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="11" width="30.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="68" t="s">
+        <v>662</v>
+      </c>
+      <c r="C3" s="45"/>
+    </row>
+    <row r="4" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="69" t="s">
+        <v>663</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>664</v>
+      </c>
+      <c r="G4" s="68" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+    </row>
+    <row r="5" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="25">
+        <v>1</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>450</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>283</v>
+      </c>
+      <c r="H5" s="70" t="s">
+        <v>284</v>
+      </c>
+      <c r="I5" s="70" t="s">
+        <v>285</v>
+      </c>
+      <c r="J5" s="70" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="25">
+        <v>2</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>454</v>
+      </c>
+      <c r="G6" s="25">
+        <v>1</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="I6" s="25">
+        <v>0</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="25">
+        <v>3</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="G7" s="25">
+        <v>2</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="25">
+        <v>0</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="25">
+        <v>4</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>461</v>
+      </c>
+      <c r="G8" s="25">
+        <v>3</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="25">
+        <v>0</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="25">
+        <v>5</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="G9" s="25">
+        <v>4</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="I9" s="25">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="25">
+        <v>6</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="G10" s="25">
+        <v>5</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="I10" s="25">
+        <v>0</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="25">
+        <v>7</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="G11" s="25">
+        <v>6</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="I11" s="25">
+        <v>1</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G12" s="25">
+        <v>7</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="25">
+        <v>1</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G13" s="25">
+        <v>8</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="25">
+        <v>1</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="G14" s="25">
+        <v>9</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="I14" s="25">
+        <v>1</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="69" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="70" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" s="71" t="s">
+        <v>363</v>
+      </c>
+      <c r="E15" s="71" t="s">
+        <v>661</v>
+      </c>
+      <c r="G15" s="25">
+        <v>10</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="I15" s="25">
+        <v>1</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="25">
+        <v>1</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="D16" s="25">
+        <v>1</v>
+      </c>
+      <c r="E16" s="25"/>
+    </row>
+    <row r="17" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="25">
+        <v>2</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="D17" s="25">
+        <v>1</v>
+      </c>
+      <c r="E17" s="25">
+        <v>1</v>
+      </c>
+      <c r="G17" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="H17" s="45"/>
+    </row>
+    <row r="18" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="25">
+        <v>3</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>453</v>
+      </c>
+      <c r="D18" s="25">
+        <v>1</v>
+      </c>
+      <c r="E18" s="25">
+        <v>2</v>
+      </c>
+      <c r="G18" s="69" t="s">
+        <v>294</v>
+      </c>
+      <c r="H18" s="69" t="s">
+        <v>665</v>
+      </c>
+      <c r="I18" s="70" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="25">
+        <v>4</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>456</v>
+      </c>
+      <c r="D19" s="25">
+        <v>2</v>
+      </c>
+      <c r="E19" s="25"/>
+      <c r="G19" s="100" t="s">
+        <v>666</v>
+      </c>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="25">
+        <v>5</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>460</v>
+      </c>
+      <c r="D20" s="25">
+        <v>2</v>
+      </c>
+      <c r="E20" s="25"/>
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="94"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="25">
+        <v>6</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>464</v>
+      </c>
+      <c r="D21" s="25">
+        <v>3</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="25">
+        <v>7</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="D22" s="25">
+        <v>3</v>
+      </c>
+      <c r="E22" s="25"/>
+      <c r="G22" s="94"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="94"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="25">
+        <v>8</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="D23" s="25">
+        <v>3</v>
+      </c>
+      <c r="E23" s="25"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="25">
+        <v>9</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="D24" s="25">
+        <v>3</v>
+      </c>
+      <c r="E24" s="25"/>
+    </row>
+    <row r="25" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="25">
+        <v>10</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="D25" s="25">
+        <v>3</v>
+      </c>
+      <c r="E25" s="25">
+        <v>8</v>
+      </c>
+      <c r="G25" s="68" t="s">
+        <v>287</v>
+      </c>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+    </row>
+    <row r="26" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="25">
+        <v>11</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="D26" s="25">
+        <v>4</v>
+      </c>
+      <c r="E26" s="25"/>
+      <c r="G26" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="H26" s="76" t="s">
+        <v>289</v>
+      </c>
+      <c r="I26" s="76" t="s">
+        <v>288</v>
+      </c>
+      <c r="J26" s="76" t="s">
+        <v>292</v>
+      </c>
+      <c r="K26" s="70" t="s">
+        <v>290</v>
+      </c>
+      <c r="L26" s="70" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="25">
+        <v>12</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>484</v>
+      </c>
+      <c r="D27" s="25">
+        <v>1</v>
+      </c>
+      <c r="E27" s="25"/>
+      <c r="G27" s="45" t="s">
+        <v>635</v>
+      </c>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="25">
+        <v>13</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="D28" s="25">
+        <v>4</v>
+      </c>
+      <c r="E28" s="25"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="94" t="s">
+        <v>667</v>
+      </c>
+      <c r="I28" s="94"/>
+      <c r="J28" s="94"/>
+      <c r="K28" s="94"/>
+      <c r="L28" s="45"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="25">
+        <v>14</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>490</v>
+      </c>
+      <c r="D29" s="25">
+        <v>5</v>
+      </c>
+      <c r="E29" s="25"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="94"/>
+      <c r="J29" s="94"/>
+      <c r="K29" s="94"/>
+      <c r="L29" s="45"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" s="25">
+        <v>15</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="D30" s="25">
+        <v>5</v>
+      </c>
+      <c r="E30" s="25"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="94"/>
+      <c r="J30" s="94"/>
+      <c r="K30" s="94"/>
+      <c r="L30" s="45"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" s="25">
+        <v>16</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="D31" s="25">
+        <v>6</v>
+      </c>
+      <c r="E31" s="25"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="94"/>
+      <c r="J31" s="94"/>
+      <c r="K31" s="94"/>
+      <c r="L31" s="45"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="25">
+        <v>17</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="D32" s="25">
+        <v>6</v>
+      </c>
+      <c r="E32" s="25"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="94"/>
+      <c r="K32" s="94"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="25">
+        <v>18</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="D33" s="25">
+        <v>5</v>
+      </c>
+      <c r="E33" s="25"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="94"/>
+      <c r="J33" s="94"/>
+      <c r="K33" s="94"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="25">
+        <v>19</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="D34" s="25">
+        <v>7</v>
+      </c>
+      <c r="E34" s="25"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="94"/>
+      <c r="K34" s="94"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="25">
+        <v>20</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="D35" s="25">
+        <v>7</v>
+      </c>
+      <c r="E35" s="25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D37" s="84" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="68" t="s">
+        <v>311</v>
+      </c>
+      <c r="D39" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="69" t="s">
+        <v>312</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="25">
+        <v>1</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="25">
+        <v>2</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="25">
+        <v>3</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="25">
+        <v>4</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="25">
+        <v>5</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="25">
+        <v>6</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="25">
+        <v>7</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="25">
+        <v>8</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="68" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B52" s="69" t="s">
+        <v>309</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="J52" s="98" t="s">
+        <v>679</v>
+      </c>
+      <c r="K52" s="98"/>
+      <c r="L52" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="25">
+        <v>1</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>681</v>
+      </c>
+      <c r="D53" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E53" s="72" t="s">
+        <v>737</v>
+      </c>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="I53" s="25" t="s">
+        <v>548</v>
+      </c>
+      <c r="J53" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K53" s="3"/>
+      <c r="L53" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="25">
+        <v>2</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>683</v>
+      </c>
+      <c r="D54" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>738</v>
+      </c>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25" t="s">
+        <v>684</v>
+      </c>
+      <c r="H54" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="I54" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="J54" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="25">
+        <v>3</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>685</v>
+      </c>
+      <c r="D55" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>739</v>
+      </c>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25" t="s">
+        <v>686</v>
+      </c>
+      <c r="H55" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="I55" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="J55" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B56" s="25">
+        <v>4</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>687</v>
+      </c>
+      <c r="D56" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>740</v>
+      </c>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25" t="s">
+        <v>688</v>
+      </c>
+      <c r="H56" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="I56" s="25" t="s">
+        <v>558</v>
+      </c>
+      <c r="J56" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B57" s="25">
+        <v>5</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>689</v>
+      </c>
+      <c r="D57" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E57" s="25" t="s">
+        <v>741</v>
+      </c>
+      <c r="F57" s="25" t="s">
+        <v>690</v>
+      </c>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="I57" s="25" t="s">
+        <v>561</v>
+      </c>
+      <c r="J57" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K57" s="3"/>
+      <c r="L57" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B58" s="25">
+        <v>6</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>691</v>
+      </c>
+      <c r="D58" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E58" s="25" t="s">
+        <v>742</v>
+      </c>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="I58" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="J58" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K58" s="3"/>
+      <c r="L58" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B59" s="25">
+        <v>7</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>692</v>
+      </c>
+      <c r="D59" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>743</v>
+      </c>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="I59" s="25" t="s">
+        <v>567</v>
+      </c>
+      <c r="J59" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K59" s="3"/>
+      <c r="L59" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B60" s="25">
+        <v>8</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>693</v>
+      </c>
+      <c r="D60" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>744</v>
+      </c>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="I60" s="25" t="s">
+        <v>570</v>
+      </c>
+      <c r="J60" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K60" s="3"/>
+      <c r="L60" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B61" s="25">
+        <v>9</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>694</v>
+      </c>
+      <c r="D61" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>745</v>
+      </c>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="I61" s="25" t="s">
+        <v>573</v>
+      </c>
+      <c r="J61" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B62" s="25">
+        <v>10</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>695</v>
+      </c>
+      <c r="D62" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>746</v>
+      </c>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="I62" s="25" t="s">
+        <v>576</v>
+      </c>
+      <c r="J62" s="85" t="s">
+        <v>682</v>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L63" s="5"/>
+    </row>
+    <row r="65" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B65" s="68" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B66" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="I66" s="98" t="s">
+        <v>697</v>
+      </c>
+      <c r="J66" s="98"/>
+      <c r="K66" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="L66" s="52" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B67" s="25">
+        <v>1</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>586</v>
+      </c>
+      <c r="D67" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E67" s="72" t="s">
+        <v>747</v>
+      </c>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25" t="s">
+        <v>588</v>
+      </c>
+      <c r="I67" s="86" t="s">
+        <v>549</v>
+      </c>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4">
+        <v>1</v>
+      </c>
+      <c r="L67" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B68" s="25">
+        <v>2</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>589</v>
+      </c>
+      <c r="D68" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E68" s="25" t="s">
+        <v>748</v>
+      </c>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25" t="s">
+        <v>684</v>
+      </c>
+      <c r="H68" s="25" t="s">
+        <v>591</v>
+      </c>
+      <c r="I68" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4">
+        <v>1</v>
+      </c>
+      <c r="L68" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B69" s="25">
+        <v>3</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>592</v>
+      </c>
+      <c r="D69" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E69" s="72" t="s">
+        <v>749</v>
+      </c>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25" t="s">
+        <v>686</v>
+      </c>
+      <c r="H69" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="I69" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4">
+        <v>1</v>
+      </c>
+      <c r="L69" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B70" s="25">
+        <v>4</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>595</v>
+      </c>
+      <c r="D70" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>750</v>
+      </c>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25" t="s">
+        <v>688</v>
+      </c>
+      <c r="H70" s="25" t="s">
+        <v>597</v>
+      </c>
+      <c r="I70" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4">
+        <v>1</v>
+      </c>
+      <c r="L70" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B71" s="25">
+        <v>5</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>598</v>
+      </c>
+      <c r="D71" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E71" s="72" t="s">
+        <v>599</v>
+      </c>
+      <c r="F71" s="25" t="s">
+        <v>690</v>
+      </c>
+      <c r="G71" s="25"/>
+      <c r="H71" s="25" t="s">
+        <v>600</v>
+      </c>
+      <c r="I71" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4">
+        <v>1</v>
+      </c>
+      <c r="L71" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B72" s="25">
+        <v>6</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>601</v>
+      </c>
+      <c r="D72" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E72" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25" t="s">
+        <v>603</v>
+      </c>
+      <c r="I72" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4">
+        <v>1</v>
+      </c>
+      <c r="L72" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B73" s="25">
+        <v>7</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>604</v>
+      </c>
+      <c r="D73" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E73" s="72" t="s">
+        <v>752</v>
+      </c>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25" t="s">
+        <v>606</v>
+      </c>
+      <c r="I73" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4">
+        <v>1</v>
+      </c>
+      <c r="L73" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B74" s="25">
+        <v>8</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>607</v>
+      </c>
+      <c r="D74" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E74" s="25" t="s">
+        <v>753</v>
+      </c>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25" t="s">
+        <v>609</v>
+      </c>
+      <c r="I74" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4">
+        <v>1</v>
+      </c>
+      <c r="L74" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B75" s="25">
+        <v>9</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>610</v>
+      </c>
+      <c r="D75" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E75" s="72" t="s">
+        <v>754</v>
+      </c>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25" t="s">
+        <v>612</v>
+      </c>
+      <c r="I75" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4">
+        <v>1</v>
+      </c>
+      <c r="L75" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B76" s="25">
+        <v>10</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>613</v>
+      </c>
+      <c r="D76" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E76" s="25" t="s">
+        <v>755</v>
+      </c>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="I76" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4">
+        <v>1</v>
+      </c>
+      <c r="L76" s="25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B77" s="25">
+        <v>11</v>
+      </c>
+      <c r="C77" s="25" t="s">
+        <v>700</v>
+      </c>
+      <c r="D77" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25" t="s">
+        <v>701</v>
+      </c>
+      <c r="I77" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4">
+        <v>1</v>
+      </c>
+      <c r="L77" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B78" s="25">
+        <v>12</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>702</v>
+      </c>
+      <c r="D78" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E78" s="72" t="s">
+        <v>757</v>
+      </c>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25" t="s">
+        <v>703</v>
+      </c>
+      <c r="I78" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4">
+        <v>1</v>
+      </c>
+      <c r="L78" s="25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B79" s="25">
+        <v>13</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>704</v>
+      </c>
+      <c r="D79" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="25" t="s">
+        <v>705</v>
+      </c>
+      <c r="I79" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4">
+        <v>1</v>
+      </c>
+      <c r="L79" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B82" s="68" t="s">
+        <v>322</v>
+      </c>
+      <c r="C82" s="45"/>
+    </row>
+    <row r="83" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B83" s="69" t="s">
+        <v>706</v>
+      </c>
+      <c r="C83" s="70" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B84" s="25">
+        <v>1</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B85" s="25">
+        <v>2</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B86" s="25">
+        <v>3</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B87" s="25">
+        <v>4</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="70"/>
+    </row>
+    <row r="89" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="68" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="69" t="s">
+        <v>299</v>
+      </c>
+      <c r="C90" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="D90" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="E90" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="F90" s="52" t="s">
+        <v>300</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H90" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="I90" s="51" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B91" s="25">
+        <v>1</v>
+      </c>
+      <c r="C91" s="25" t="s">
+        <v>709</v>
+      </c>
+      <c r="D91" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E91" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="F91" s="25">
+        <v>1</v>
+      </c>
+      <c r="G91" s="72" t="s">
+        <v>517</v>
+      </c>
+      <c r="H91" s="25">
+        <v>1</v>
+      </c>
+      <c r="I91" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B92" s="25">
+        <v>2</v>
+      </c>
+      <c r="C92" s="25" t="s">
+        <v>710</v>
+      </c>
+      <c r="D92" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E92" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="F92" s="25">
+        <v>2</v>
+      </c>
+      <c r="G92" s="72" t="s">
+        <v>519</v>
+      </c>
+      <c r="H92" s="25">
+        <v>1</v>
+      </c>
+      <c r="I92" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B93" s="25">
+        <v>3</v>
+      </c>
+      <c r="C93" s="25" t="s">
+        <v>711</v>
+      </c>
+      <c r="D93" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E93" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="F93" s="25">
+        <v>3</v>
+      </c>
+      <c r="G93" s="72" t="s">
+        <v>521</v>
+      </c>
+      <c r="H93" s="25">
+        <v>2</v>
+      </c>
+      <c r="I93" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B94" s="25">
+        <v>4</v>
+      </c>
+      <c r="C94" s="25" t="s">
+        <v>712</v>
+      </c>
+      <c r="D94" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E94" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="F94" s="25">
+        <v>4</v>
+      </c>
+      <c r="G94" s="72" t="s">
+        <v>523</v>
+      </c>
+      <c r="H94" s="25">
+        <v>2</v>
+      </c>
+      <c r="I94" s="25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B95" s="25">
+        <v>5</v>
+      </c>
+      <c r="C95" s="25" t="s">
+        <v>713</v>
+      </c>
+      <c r="D95" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E95" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="F95" s="25">
+        <v>5</v>
+      </c>
+      <c r="G95" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="H95" s="25">
+        <v>3</v>
+      </c>
+      <c r="I95" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B96" s="25">
+        <v>6</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>714</v>
+      </c>
+      <c r="D96" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E96" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="F96" s="25">
+        <v>6</v>
+      </c>
+      <c r="G96" s="72" t="s">
+        <v>519</v>
+      </c>
+      <c r="H96" s="25">
+        <v>3</v>
+      </c>
+      <c r="I96" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B97" s="25">
+        <v>7</v>
+      </c>
+      <c r="C97" s="25" t="s">
+        <v>715</v>
+      </c>
+      <c r="D97" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E97" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="F97" s="25">
+        <v>7</v>
+      </c>
+      <c r="G97" s="72" t="s">
+        <v>521</v>
+      </c>
+      <c r="H97" s="25">
+        <v>4</v>
+      </c>
+      <c r="I97" s="25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B98" s="25">
+        <v>8</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>716</v>
+      </c>
+      <c r="D98" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E98" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="F98" s="25">
+        <v>8</v>
+      </c>
+      <c r="G98" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="H98" s="25">
+        <v>4</v>
+      </c>
+      <c r="I98" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B99" s="25">
+        <v>9</v>
+      </c>
+      <c r="C99" s="25" t="s">
+        <v>717</v>
+      </c>
+      <c r="D99" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E99" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="F99" s="25">
+        <v>1</v>
+      </c>
+      <c r="G99" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="H99" s="25">
+        <v>4</v>
+      </c>
+      <c r="I99" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B100" s="25">
+        <v>10</v>
+      </c>
+      <c r="C100" s="25" t="s">
+        <v>718</v>
+      </c>
+      <c r="D100" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E100" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="F100" s="25">
+        <v>2</v>
+      </c>
+      <c r="G100" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="H100" s="25">
+        <v>4</v>
+      </c>
+      <c r="I100" s="25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="45" t="s">
+        <v>719</v>
+      </c>
+      <c r="B101" s="87">
+        <v>11</v>
+      </c>
+      <c r="C101" s="25" t="s">
+        <v>720</v>
+      </c>
+      <c r="D101" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E101" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="F101" s="25">
+        <v>9</v>
+      </c>
+      <c r="G101" s="72" t="s">
+        <v>532</v>
+      </c>
+      <c r="H101" s="25">
+        <v>3</v>
+      </c>
+      <c r="I101" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="45" t="s">
+        <v>719</v>
+      </c>
+      <c r="B102" s="87">
+        <v>12</v>
+      </c>
+      <c r="C102" s="25" t="s">
+        <v>721</v>
+      </c>
+      <c r="D102" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E102" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="F102" s="25">
+        <v>10</v>
+      </c>
+      <c r="G102" s="72" t="s">
+        <v>534</v>
+      </c>
+      <c r="H102" s="25">
+        <v>3</v>
+      </c>
+      <c r="I102" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="45" t="s">
+        <v>719</v>
+      </c>
+      <c r="B103" s="87">
+        <v>13</v>
+      </c>
+      <c r="C103" s="25" t="s">
+        <v>722</v>
+      </c>
+      <c r="D103" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="E103" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="F103" s="25">
+        <v>5</v>
+      </c>
+      <c r="G103" s="72" t="s">
+        <v>536</v>
+      </c>
+      <c r="H103" s="25">
+        <v>1</v>
+      </c>
+      <c r="I103" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B107" s="68" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B108" s="69" t="s">
+        <v>335</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E108" s="52" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B110" s="94" t="s">
+        <v>723</v>
+      </c>
+      <c r="C110" s="93"/>
+      <c r="D110" s="93"/>
+      <c r="E110" s="93"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B111" s="93"/>
+      <c r="C111" s="93"/>
+      <c r="D111" s="93"/>
+      <c r="E111" s="93"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B112" s="93"/>
+      <c r="C112" s="93"/>
+      <c r="D112" s="93"/>
+      <c r="E112" s="93"/>
+    </row>
+    <row r="113" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="93"/>
+      <c r="C113" s="93"/>
+      <c r="D113" s="93"/>
+      <c r="E113" s="93"/>
+      <c r="F113" s="45"/>
+      <c r="G113" s="45"/>
+      <c r="H113" s="45"/>
+      <c r="I113" s="45"/>
+    </row>
+    <row r="114" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B114" s="93"/>
+      <c r="C114" s="93"/>
+      <c r="D114" s="93"/>
+      <c r="E114" s="93"/>
+      <c r="F114" s="88"/>
+      <c r="G114" s="88"/>
+      <c r="H114" s="89"/>
+      <c r="I114" s="89"/>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B115" s="93"/>
+      <c r="C115" s="93"/>
+      <c r="D115" s="93"/>
+      <c r="E115" s="93"/>
+      <c r="G115" s="45"/>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D116" s="45"/>
+      <c r="G116" s="45"/>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="D117" s="45"/>
+      <c r="G117" s="45"/>
+    </row>
+    <row r="118" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B118" s="68" t="s">
+        <v>359</v>
+      </c>
+      <c r="C118" s="45"/>
+      <c r="D118" s="45"/>
+      <c r="G118" s="45"/>
+    </row>
+    <row r="119" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B119" s="69" t="s">
+        <v>340</v>
+      </c>
+      <c r="C119" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="D119" s="70" t="s">
+        <v>342</v>
+      </c>
+      <c r="G119" s="45"/>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B120" s="99" t="s">
+        <v>646</v>
+      </c>
+      <c r="C120" s="99"/>
+      <c r="D120" s="99"/>
+      <c r="G120" s="45"/>
+    </row>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B121" s="99"/>
+      <c r="C121" s="99"/>
+      <c r="D121" s="99"/>
+      <c r="G121" s="45"/>
+    </row>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B122" s="99"/>
+      <c r="C122" s="99"/>
+      <c r="D122" s="99"/>
+      <c r="G122" s="45"/>
+    </row>
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B123" s="25">
+        <v>1</v>
+      </c>
+      <c r="C123" s="25">
+        <v>1</v>
+      </c>
+      <c r="D123" s="25">
+        <v>2</v>
+      </c>
+      <c r="G123" s="45"/>
+    </row>
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B124" s="25">
+        <v>1</v>
+      </c>
+      <c r="C124" s="25">
+        <v>3</v>
+      </c>
+      <c r="D124" s="25">
+        <v>4</v>
+      </c>
+      <c r="G124" s="45"/>
+    </row>
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B125" s="25">
+        <v>2</v>
+      </c>
+      <c r="C125" s="25">
+        <v>4</v>
+      </c>
+      <c r="D125" s="25">
+        <v>2</v>
+      </c>
+      <c r="G125" s="45"/>
+    </row>
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B126" s="25">
+        <v>2</v>
+      </c>
+      <c r="C126" s="25">
+        <v>5</v>
+      </c>
+      <c r="D126" s="25">
+        <v>2</v>
+      </c>
+      <c r="G126" s="45"/>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B127" s="25">
+        <v>3</v>
+      </c>
+      <c r="C127" s="25">
+        <v>6</v>
+      </c>
+      <c r="D127" s="25">
+        <v>4</v>
+      </c>
+      <c r="G127" s="45"/>
+    </row>
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B128" s="25">
+        <v>3</v>
+      </c>
+      <c r="C128" s="25">
+        <v>2</v>
+      </c>
+      <c r="D128" s="25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B129" s="25">
+        <v>4</v>
+      </c>
+      <c r="C129" s="25">
+        <v>8</v>
+      </c>
+      <c r="D129" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B130" s="25">
+        <v>4</v>
+      </c>
+      <c r="C130" s="25">
+        <v>12</v>
+      </c>
+      <c r="D130" s="25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B131" s="25">
+        <v>5</v>
+      </c>
+      <c r="C131" s="25">
+        <v>88</v>
+      </c>
+      <c r="D131" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B132" s="25">
+        <v>5</v>
+      </c>
+      <c r="C132" s="25">
+        <v>22</v>
+      </c>
+      <c r="D132" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B133" s="25">
+        <v>5</v>
+      </c>
+      <c r="C133" s="25">
+        <v>11</v>
+      </c>
+      <c r="D133" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B134" s="25">
+        <v>5</v>
+      </c>
+      <c r="C134" s="25">
+        <v>33</v>
+      </c>
+      <c r="D134" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B135" s="25">
+        <v>6</v>
+      </c>
+      <c r="C135" s="25">
+        <v>2</v>
+      </c>
+      <c r="D135" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B136" s="25">
+        <v>7</v>
+      </c>
+      <c r="C136" s="25">
+        <v>1</v>
+      </c>
+      <c r="D136" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B137" s="25">
+        <v>8</v>
+      </c>
+      <c r="C137" s="25">
+        <v>27</v>
+      </c>
+      <c r="D137" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B138" s="25">
+        <v>8</v>
+      </c>
+      <c r="C138" s="25">
+        <v>23</v>
+      </c>
+      <c r="D138" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B139" s="25">
+        <v>8</v>
+      </c>
+      <c r="C139" s="25">
+        <v>98</v>
+      </c>
+      <c r="D139" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B140" s="25">
+        <v>9</v>
+      </c>
+      <c r="C140" s="25">
+        <v>100</v>
+      </c>
+      <c r="D140" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B141" s="25">
+        <v>9</v>
+      </c>
+      <c r="C141" s="25">
+        <v>11</v>
+      </c>
+      <c r="D141" s="25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B142" s="25">
+        <v>9</v>
+      </c>
+      <c r="C142" s="25">
+        <v>45</v>
+      </c>
+      <c r="D142" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B143" s="25">
+        <v>9</v>
+      </c>
+      <c r="C143" s="25">
+        <v>22</v>
+      </c>
+      <c r="D143" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B144" s="25">
+        <v>9</v>
+      </c>
+      <c r="C144" s="25">
+        <v>32</v>
+      </c>
+      <c r="D144" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B145" s="25">
+        <v>10</v>
+      </c>
+      <c r="C145" s="25">
+        <v>18</v>
+      </c>
+      <c r="D145" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B146" s="25">
+        <v>10</v>
+      </c>
+      <c r="C146" s="25">
+        <v>29</v>
+      </c>
+      <c r="D146" s="25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B147" s="25">
+        <v>11</v>
+      </c>
+      <c r="C147" s="25">
+        <v>33</v>
+      </c>
+      <c r="D147" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B148" s="25">
+        <v>11</v>
+      </c>
+      <c r="C148" s="25">
+        <v>65</v>
+      </c>
+      <c r="D148" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B149" s="25">
+        <v>11</v>
+      </c>
+      <c r="C149" s="25">
+        <v>1</v>
+      </c>
+      <c r="D149" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B150" s="25">
+        <v>11</v>
+      </c>
+      <c r="C150" s="25">
+        <v>2</v>
+      </c>
+      <c r="D150" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B151" s="25">
+        <v>11</v>
+      </c>
+      <c r="C151" s="25">
+        <v>5</v>
+      </c>
+      <c r="D151" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B152" s="25">
+        <v>11</v>
+      </c>
+      <c r="C152" s="25">
+        <v>7</v>
+      </c>
+      <c r="D152" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B153" s="25">
+        <v>12</v>
+      </c>
+      <c r="C153" s="25">
+        <v>55</v>
+      </c>
+      <c r="D153" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B154" s="25">
+        <v>13</v>
+      </c>
+      <c r="C154" s="25">
+        <v>92</v>
+      </c>
+      <c r="D154" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B155" s="25">
+        <v>13</v>
+      </c>
+      <c r="C155" s="25">
+        <v>14</v>
+      </c>
+      <c r="D155" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B159" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B160" s="53" t="s">
+        <v>361</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D160" s="52" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B161" s="25">
+        <v>1</v>
+      </c>
+      <c r="C161" s="25"/>
+      <c r="D161" s="25"/>
+    </row>
+    <row r="162" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B162" s="25">
+        <v>2</v>
+      </c>
+      <c r="C162" s="25"/>
+      <c r="D162" s="25"/>
+    </row>
+    <row r="163" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B163" s="25">
+        <v>3</v>
+      </c>
+      <c r="C163" s="25"/>
+      <c r="D163" s="25"/>
+    </row>
+    <row r="164" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B164" s="25">
+        <v>4</v>
+      </c>
+      <c r="C164" s="25"/>
+      <c r="D164" s="25"/>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B165" s="25">
+        <v>5</v>
+      </c>
+      <c r="C165" s="72" t="s">
+        <v>724</v>
+      </c>
+      <c r="D165" s="25" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B166" s="25">
+        <v>6</v>
+      </c>
+      <c r="C166" s="25"/>
+      <c r="D166" s="72" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B167" s="25">
+        <v>7</v>
+      </c>
+      <c r="C167" s="25"/>
+      <c r="D167" s="25"/>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B168" s="25">
+        <v>8</v>
+      </c>
+      <c r="C168" s="25"/>
+      <c r="D168" s="25"/>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B169" s="25">
+        <v>9</v>
+      </c>
+      <c r="C169" s="25"/>
+      <c r="D169" s="25"/>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B170" s="25">
+        <v>10</v>
+      </c>
+      <c r="C170" s="25"/>
+      <c r="D170" s="25"/>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B173" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B174" s="54" t="s">
+        <v>344</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B175" s="4">
+        <v>1</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="D175" s="4">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B176" s="4">
+        <v>2</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="D176" s="4">
+        <v>23456</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B177" s="4">
+        <v>3</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="D177" s="4">
+        <v>34567</v>
+      </c>
+    </row>
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B178" s="4">
+        <v>4</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D178" s="4">
+        <v>72727</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B179" s="4">
+        <v>5</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="D179" s="4">
+        <v>28282</v>
+      </c>
+    </row>
+    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B182" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C182" s="45"/>
+      <c r="D182" s="45"/>
+      <c r="E182" s="45"/>
+      <c r="F182" s="45"/>
+    </row>
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B183" s="53" t="s">
+        <v>351</v>
+      </c>
+      <c r="C183" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F183" s="52" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B184" s="45" t="s">
+        <v>731</v>
+      </c>
+      <c r="C184" s="45" t="s">
+        <v>732</v>
+      </c>
+      <c r="D184" s="45" t="s">
+        <v>733</v>
+      </c>
+      <c r="E184" s="45" t="s">
+        <v>734</v>
+      </c>
+      <c r="F184" s="45" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B185" s="45"/>
+      <c r="C185" s="45"/>
+      <c r="D185" s="45"/>
+      <c r="E185" s="45"/>
+      <c r="F185" s="45"/>
+    </row>
+    <row r="186" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B186" s="45">
+        <v>1</v>
+      </c>
+      <c r="C186" s="45">
+        <v>1</v>
+      </c>
+      <c r="D186" s="45"/>
+      <c r="E186" s="45"/>
+      <c r="F186" s="45"/>
+    </row>
+    <row r="187" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B187" s="45">
+        <v>2</v>
+      </c>
+      <c r="C187" s="45">
+        <v>2</v>
+      </c>
+      <c r="D187" s="45"/>
+      <c r="E187" s="45"/>
+      <c r="F187" s="45"/>
+    </row>
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B188" s="45">
+        <v>3</v>
+      </c>
+      <c r="C188" s="45">
+        <v>3</v>
+      </c>
+      <c r="D188" s="45"/>
+      <c r="E188" s="45"/>
+      <c r="F188" s="45"/>
+    </row>
+    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B189" s="45">
+        <v>4</v>
+      </c>
+      <c r="C189" s="45">
+        <v>4</v>
+      </c>
+      <c r="D189" s="45"/>
+      <c r="E189" s="45"/>
+      <c r="F189" s="45"/>
+    </row>
+    <row r="190" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B190" s="45">
+        <v>5</v>
+      </c>
+      <c r="C190" s="45">
+        <v>5</v>
+      </c>
+      <c r="D190" s="45"/>
+      <c r="E190" s="45"/>
+      <c r="F190" s="45"/>
+    </row>
+    <row r="191" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B191" s="45">
+        <v>6</v>
+      </c>
+      <c r="C191" s="45">
+        <v>6</v>
+      </c>
+      <c r="D191" s="45"/>
+      <c r="E191" s="45"/>
+      <c r="F191" s="45"/>
+    </row>
+    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B192" s="45"/>
+      <c r="C192" s="45" t="s">
+        <v>736</v>
+      </c>
+      <c r="D192" s="45"/>
+      <c r="E192" s="45"/>
+      <c r="F192" s="45"/>
+    </row>
+    <row r="193" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B193" s="45">
+        <v>10</v>
+      </c>
+      <c r="C193" s="45">
+        <v>10</v>
+      </c>
+      <c r="D193" s="45"/>
+      <c r="E193" s="45"/>
+      <c r="F193" s="45"/>
+    </row>
+    <row r="194" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B194" s="45">
+        <v>1</v>
+      </c>
+      <c r="C194" s="45">
+        <v>11</v>
+      </c>
+      <c r="D194" s="45"/>
+      <c r="E194" s="45"/>
+      <c r="F194" s="45"/>
+    </row>
+    <row r="195" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B195" s="45"/>
+      <c r="C195" s="45" t="s">
+        <v>736</v>
+      </c>
+      <c r="D195" s="45"/>
+      <c r="E195" s="45"/>
+      <c r="F195" s="45"/>
+    </row>
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B196" s="45">
+        <v>10</v>
+      </c>
+      <c r="C196" s="45">
+        <v>20</v>
+      </c>
+      <c r="D196" s="5"/>
+      <c r="E196" s="5"/>
+      <c r="F196" s="5"/>
+    </row>
+    <row r="197" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B197" s="5"/>
+      <c r="C197" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="D197" s="5"/>
+      <c r="E197" s="5"/>
+      <c r="F197" s="5"/>
+    </row>
+    <row r="198" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B198" s="90">
+        <v>3</v>
+      </c>
+      <c r="C198" s="90">
+        <v>1</v>
+      </c>
+      <c r="D198" s="5"/>
+      <c r="E198" s="5"/>
+      <c r="F198" s="5"/>
+    </row>
+    <row r="199" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B199" s="90">
+        <v>6</v>
+      </c>
+      <c r="C199" s="90">
+        <v>5</v>
+      </c>
+      <c r="D199" s="5"/>
+      <c r="E199" s="5"/>
+      <c r="F199" s="5"/>
+    </row>
+    <row r="200" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B200" s="90">
+        <v>9</v>
+      </c>
+      <c r="C200" s="90">
+        <v>10</v>
+      </c>
+      <c r="D200" s="5"/>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5"/>
+    </row>
+    <row r="201" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B201" s="5"/>
+      <c r="C201" s="5"/>
+      <c r="D201" s="5"/>
+      <c r="E201" s="5"/>
+      <c r="F201" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="I66:J66"/>
+    <mergeCell ref="B110:E115"/>
+    <mergeCell ref="B120:D122"/>
+    <mergeCell ref="G19:I22"/>
+    <mergeCell ref="H28:K34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96667ABA-8E97-4335-ACA2-0083A76758B8}">
+  <dimension ref="B3:AI135"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="14" width="28.7109375" customWidth="1"/>
+    <col min="33" max="33" width="17.7109375" customWidth="1"/>
+    <col min="34" max="34" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="68" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+    </row>
+    <row r="4" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="69" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="70" t="s">
+        <v>439</v>
+      </c>
+      <c r="E4" s="71" t="s">
+        <v>363</v>
+      </c>
+      <c r="F4" s="45"/>
+      <c r="G4" s="68" t="s">
+        <v>440</v>
+      </c>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="68" t="s">
+        <v>441</v>
+      </c>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="68" t="s">
+        <v>442</v>
+      </c>
+      <c r="N4" s="45"/>
+    </row>
+    <row r="5" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="25">
+        <v>1</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="D5" s="25">
+        <v>100</v>
+      </c>
+      <c r="E5" s="25">
+        <v>1</v>
+      </c>
+      <c r="F5" s="45"/>
+      <c r="G5" s="69" t="s">
+        <v>444</v>
+      </c>
+      <c r="H5" s="70" t="s">
+        <v>445</v>
+      </c>
+      <c r="I5" s="45"/>
+      <c r="J5" s="69" t="s">
+        <v>446</v>
+      </c>
+      <c r="K5" s="70" t="s">
+        <v>447</v>
+      </c>
+      <c r="L5" s="45"/>
+      <c r="M5" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="N5" s="70" t="s">
+        <v>448</v>
+      </c>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+    </row>
+    <row r="6" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B6" s="25">
+        <v>2</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="D6" s="25">
+        <v>60</v>
+      </c>
+      <c r="E6" s="25">
+        <v>1</v>
+      </c>
+      <c r="F6" s="45"/>
+      <c r="G6" s="25">
+        <v>1</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>450</v>
+      </c>
+      <c r="I6" s="45"/>
+      <c r="J6" s="25">
+        <v>1</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>451</v>
+      </c>
+      <c r="L6" s="45"/>
+      <c r="M6" s="25">
+        <v>1</v>
+      </c>
+      <c r="N6" s="25" t="s">
+        <v>452</v>
+      </c>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+    </row>
+    <row r="7" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B7" s="25">
+        <v>3</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>453</v>
+      </c>
+      <c r="D7" s="25">
+        <v>80</v>
+      </c>
+      <c r="E7" s="25">
+        <v>1</v>
+      </c>
+      <c r="F7" s="45"/>
+      <c r="G7" s="25">
+        <v>2</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>454</v>
+      </c>
+      <c r="I7" s="45"/>
+      <c r="J7" s="25">
+        <v>2</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="L7" s="45"/>
+      <c r="M7" s="25">
+        <v>2</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>455</v>
+      </c>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+    </row>
+    <row r="8" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B8" s="25">
+        <v>4</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>456</v>
+      </c>
+      <c r="D8" s="25">
+        <v>40</v>
+      </c>
+      <c r="E8" s="25">
+        <v>2</v>
+      </c>
+      <c r="F8" s="45"/>
+      <c r="G8" s="25">
+        <v>3</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="I8" s="45"/>
+      <c r="J8" s="25">
+        <v>3</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>458</v>
+      </c>
+      <c r="L8" s="45"/>
+      <c r="M8" s="25">
+        <v>3</v>
+      </c>
+      <c r="N8" s="25" t="s">
+        <v>459</v>
+      </c>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+    </row>
+    <row r="9" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B9" s="25">
+        <v>5</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>460</v>
+      </c>
+      <c r="D9" s="25">
+        <v>60</v>
+      </c>
+      <c r="E9" s="25">
+        <v>2</v>
+      </c>
+      <c r="F9" s="45"/>
+      <c r="G9" s="25">
+        <v>4</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>461</v>
+      </c>
+      <c r="I9" s="45"/>
+      <c r="J9" s="25">
+        <v>4</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>462</v>
+      </c>
+      <c r="L9" s="45"/>
+      <c r="M9" s="25">
+        <v>4</v>
+      </c>
+      <c r="N9" s="25" t="s">
+        <v>463</v>
+      </c>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B10" s="25">
+        <v>6</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>464</v>
+      </c>
+      <c r="D10" s="25">
+        <v>180</v>
+      </c>
+      <c r="E10" s="25">
+        <v>3</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="G10" s="25">
+        <v>5</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="I10" s="45"/>
+      <c r="J10" s="25">
+        <v>5</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="L10" s="45"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
+      <c r="P10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B11" s="25">
+        <v>7</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>467</v>
+      </c>
+      <c r="D11" s="25">
+        <v>80</v>
+      </c>
+      <c r="E11" s="25">
+        <v>3</v>
+      </c>
+      <c r="F11" s="45"/>
+      <c r="G11" s="25">
+        <v>6</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="I11" s="45"/>
+      <c r="J11" s="25">
+        <v>6</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="L11" s="45"/>
+      <c r="M11" s="45"/>
+      <c r="N11" s="45"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B12" s="25">
+        <v>8</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="D12" s="25">
+        <v>126</v>
+      </c>
+      <c r="E12" s="25">
+        <v>3</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="25">
+        <v>7</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="I12" s="45"/>
+      <c r="J12" s="25">
+        <v>7</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B13" s="25">
+        <v>9</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="D13" s="25">
+        <v>142</v>
+      </c>
+      <c r="E13" s="25">
+        <v>3</v>
+      </c>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="45"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+    </row>
+    <row r="14" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="25">
+        <v>10</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="D14" s="25">
+        <v>195</v>
+      </c>
+      <c r="E14" s="25">
+        <v>3</v>
+      </c>
+      <c r="F14" s="45"/>
+      <c r="G14" s="68" t="s">
+        <v>475</v>
+      </c>
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="68" t="s">
+        <v>476</v>
+      </c>
+      <c r="K14" s="45"/>
+      <c r="L14" s="45"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+    </row>
+    <row r="15" spans="2:25" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="25">
+        <v>11</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>477</v>
+      </c>
+      <c r="D15" s="25">
+        <v>180</v>
+      </c>
+      <c r="E15" s="25">
+        <v>4</v>
+      </c>
+      <c r="F15" s="45"/>
+      <c r="G15" s="69" t="s">
+        <v>478</v>
+      </c>
+      <c r="H15" s="70" t="s">
+        <v>479</v>
+      </c>
+      <c r="I15" s="45"/>
+      <c r="J15" s="69" t="s">
+        <v>480</v>
+      </c>
+      <c r="K15" s="70" t="s">
+        <v>481</v>
+      </c>
+      <c r="L15" s="70" t="s">
+        <v>482</v>
+      </c>
+      <c r="M15" s="70" t="s">
+        <v>483</v>
+      </c>
+      <c r="N15" s="45"/>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B16" s="25">
+        <v>12</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>484</v>
+      </c>
+      <c r="D16" s="25">
+        <v>88</v>
+      </c>
+      <c r="E16" s="25">
+        <v>1</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="25">
+        <v>1</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="I16" s="45"/>
+      <c r="J16" s="25">
+        <v>1</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="L16" s="25">
+        <v>0</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="N16" s="45"/>
+    </row>
+    <row r="17" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B17" s="25">
+        <v>13</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="D17" s="25">
+        <v>200</v>
+      </c>
+      <c r="E17" s="25">
+        <v>4</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="25">
+        <v>2</v>
+      </c>
+      <c r="H17" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="I17" s="45"/>
+      <c r="J17" s="25">
+        <v>2</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="25">
+        <v>0</v>
+      </c>
+      <c r="M17" s="25" t="s">
+        <v>489</v>
+      </c>
+      <c r="N17" s="45"/>
+    </row>
+    <row r="18" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B18" s="25">
+        <v>14</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>490</v>
+      </c>
+      <c r="D18" s="25">
+        <v>120</v>
+      </c>
+      <c r="E18" s="25">
+        <v>5</v>
+      </c>
+      <c r="F18" s="45"/>
+      <c r="G18" s="25">
+        <v>3</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="I18" s="45"/>
+      <c r="J18" s="25">
+        <v>3</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="L18" s="25">
+        <v>0</v>
+      </c>
+      <c r="M18" s="25" t="s">
+        <v>492</v>
+      </c>
+      <c r="N18" s="45"/>
+      <c r="T18" s="19"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5"/>
+    </row>
+    <row r="19" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B19" s="25">
+        <v>15</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="D19" s="25">
+        <v>160</v>
+      </c>
+      <c r="E19" s="25">
+        <v>5</v>
+      </c>
+      <c r="F19" s="45"/>
+      <c r="G19" s="25">
+        <v>4</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>494</v>
+      </c>
+      <c r="I19" s="45"/>
+      <c r="J19" s="25">
+        <v>4</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="L19" s="25">
+        <v>0</v>
+      </c>
+      <c r="M19" s="25" t="s">
+        <v>495</v>
+      </c>
+      <c r="N19" s="45"/>
+      <c r="P19" s="102"/>
+      <c r="Q19" s="102"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+    </row>
+    <row r="20" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B20" s="25">
+        <v>16</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="D20" s="25">
+        <v>140</v>
+      </c>
+      <c r="E20" s="25">
+        <v>6</v>
+      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="25">
+        <v>5</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="L20" s="25">
+        <v>0</v>
+      </c>
+      <c r="M20" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="N20" s="45"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="102"/>
+      <c r="R20" s="102"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+    </row>
+    <row r="21" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B21" s="25">
+        <v>17</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="D21" s="25">
+        <v>170</v>
+      </c>
+      <c r="E21" s="25">
+        <v>6</v>
+      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="25">
+        <v>6</v>
+      </c>
+      <c r="K21" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="L21" s="25">
+        <v>1</v>
+      </c>
+      <c r="M21" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="N21" s="45"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="102"/>
+      <c r="R21" s="102"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+    </row>
+    <row r="22" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B22" s="25">
+        <v>18</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="D22" s="25">
+        <v>120</v>
+      </c>
+      <c r="E22" s="25">
+        <v>5</v>
+      </c>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="25">
+        <v>7</v>
+      </c>
+      <c r="K22" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="L22" s="25">
+        <v>1</v>
+      </c>
+      <c r="M22" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="N22" s="45"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="102"/>
+      <c r="R22" s="102"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+    </row>
+    <row r="23" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B23" s="25">
+        <v>19</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="D23" s="25">
+        <v>175</v>
+      </c>
+      <c r="E23" s="25">
+        <v>7</v>
+      </c>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="25">
+        <v>8</v>
+      </c>
+      <c r="K23" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="L23" s="25">
+        <v>1</v>
+      </c>
+      <c r="M23" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="N23" s="45"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="102"/>
+      <c r="R23" s="102"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5"/>
+    </row>
+    <row r="24" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B24" s="25">
+        <v>20</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="D24" s="25">
+        <v>186</v>
+      </c>
+      <c r="E24" s="25">
+        <v>7</v>
+      </c>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="25">
+        <v>9</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="L24" s="25">
+        <v>1</v>
+      </c>
+      <c r="M24" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="N24" s="45"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="102"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+    </row>
+    <row r="25" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="25">
+        <v>10</v>
+      </c>
+      <c r="K25" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="L25" s="25">
+        <v>1</v>
+      </c>
+      <c r="M25" s="25" t="s">
+        <v>506</v>
+      </c>
+      <c r="N25" s="45"/>
+    </row>
+    <row r="26" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+    </row>
+    <row r="27" spans="2:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="68" t="s">
+        <v>507</v>
+      </c>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45" t="s">
+        <v>508</v>
+      </c>
+      <c r="H27" s="45"/>
+      <c r="I27" s="45"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+    </row>
+    <row r="28" spans="2:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="69" t="s">
+        <v>509</v>
+      </c>
+      <c r="C28" s="70" t="s">
+        <v>510</v>
+      </c>
+      <c r="D28" s="70" t="s">
+        <v>511</v>
+      </c>
+      <c r="E28" s="70" t="s">
+        <v>512</v>
+      </c>
+      <c r="F28" s="70" t="s">
+        <v>513</v>
+      </c>
+      <c r="G28" s="70" t="s">
+        <v>514</v>
+      </c>
+      <c r="H28" s="71" t="s">
+        <v>515</v>
+      </c>
+      <c r="I28" s="71" t="s">
+        <v>516</v>
+      </c>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="19"/>
+      <c r="AD28" s="43"/>
+    </row>
+    <row r="29" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B29" s="25">
+        <v>1</v>
+      </c>
+      <c r="C29" s="72" t="s">
+        <v>517</v>
+      </c>
+      <c r="D29" s="25">
+        <v>20</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="F29" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G29" s="25">
+        <v>0</v>
+      </c>
+      <c r="H29" s="25">
+        <v>1</v>
+      </c>
+      <c r="I29" s="25">
+        <v>1</v>
+      </c>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
+      <c r="P29" s="5"/>
+      <c r="T29" s="45"/>
+      <c r="U29" s="45"/>
+      <c r="V29" s="45"/>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="AA29" s="73"/>
+      <c r="AB29" s="5"/>
+      <c r="AC29" s="5"/>
+      <c r="AD29" s="73"/>
+      <c r="AF29" s="73"/>
+      <c r="AG29" s="5"/>
+      <c r="AH29" s="5"/>
+      <c r="AI29" s="73"/>
+    </row>
+    <row r="30" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B30" s="25">
+        <v>2</v>
+      </c>
+      <c r="C30" s="72" t="s">
+        <v>519</v>
+      </c>
+      <c r="D30" s="25">
+        <v>20</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="F30" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G30" s="25">
+        <v>0</v>
+      </c>
+      <c r="H30" s="25">
+        <v>1</v>
+      </c>
+      <c r="I30" s="25">
+        <v>2</v>
+      </c>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="T30" s="45"/>
+      <c r="U30" s="45"/>
+      <c r="V30" s="45"/>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="AA30" s="73"/>
+      <c r="AB30" s="74"/>
+      <c r="AC30" s="5"/>
+      <c r="AD30" s="73"/>
+      <c r="AF30" s="73"/>
+      <c r="AG30" s="74"/>
+      <c r="AH30" s="5"/>
+      <c r="AI30" s="73"/>
+    </row>
+    <row r="31" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B31" s="25">
+        <v>3</v>
+      </c>
+      <c r="C31" s="72" t="s">
+        <v>521</v>
+      </c>
+      <c r="D31" s="25">
+        <v>20</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="F31" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G31" s="25">
+        <v>0</v>
+      </c>
+      <c r="H31" s="25">
+        <v>2</v>
+      </c>
+      <c r="I31" s="25">
+        <v>3</v>
+      </c>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="45"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="T31" s="45"/>
+      <c r="U31" s="45"/>
+      <c r="V31" s="45"/>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="AA31" s="73"/>
+      <c r="AB31" s="74"/>
+      <c r="AC31" s="5"/>
+      <c r="AD31" s="73"/>
+      <c r="AF31" s="73"/>
+      <c r="AG31" s="74"/>
+      <c r="AH31" s="5"/>
+      <c r="AI31" s="73"/>
+    </row>
+    <row r="32" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B32" s="25">
+        <v>4</v>
+      </c>
+      <c r="C32" s="72" t="s">
+        <v>523</v>
+      </c>
+      <c r="D32" s="25">
+        <v>30</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="F32" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G32" s="25">
+        <v>0</v>
+      </c>
+      <c r="H32" s="25">
+        <v>2</v>
+      </c>
+      <c r="I32" s="25">
+        <v>4</v>
+      </c>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="45"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="T32" s="45"/>
+      <c r="U32" s="45"/>
+      <c r="V32" s="45"/>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="AA32" s="73"/>
+      <c r="AB32" s="74"/>
+      <c r="AC32" s="5"/>
+      <c r="AD32" s="73"/>
+      <c r="AF32" s="73"/>
+      <c r="AG32" s="74"/>
+      <c r="AH32" s="5"/>
+      <c r="AI32" s="73"/>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B33" s="25">
+        <v>5</v>
+      </c>
+      <c r="C33" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="D33" s="25">
+        <v>30</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="F33" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G33" s="25">
+        <v>0</v>
+      </c>
+      <c r="H33" s="25">
+        <v>3</v>
+      </c>
+      <c r="I33" s="25">
+        <v>5</v>
+      </c>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="45"/>
+      <c r="N33" s="45"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="T33" s="45"/>
+      <c r="U33" s="45"/>
+      <c r="V33" s="45"/>
+      <c r="AA33" s="73"/>
+      <c r="AB33" s="74"/>
+      <c r="AC33" s="5"/>
+      <c r="AD33" s="73"/>
+      <c r="AF33" s="73"/>
+      <c r="AG33" s="74"/>
+      <c r="AH33" s="5"/>
+      <c r="AI33" s="73"/>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B34" s="25">
+        <v>6</v>
+      </c>
+      <c r="C34" s="72" t="s">
+        <v>519</v>
+      </c>
+      <c r="D34" s="25">
+        <v>40</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="F34" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G34" s="25">
+        <v>0</v>
+      </c>
+      <c r="H34" s="25">
+        <v>3</v>
+      </c>
+      <c r="I34" s="25">
+        <v>6</v>
+      </c>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="45"/>
+      <c r="N34" s="45"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="T34" s="75"/>
+      <c r="U34" s="75"/>
+      <c r="V34" s="45"/>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B35" s="25">
+        <v>7</v>
+      </c>
+      <c r="C35" s="72" t="s">
+        <v>521</v>
+      </c>
+      <c r="D35" s="25">
+        <v>40</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="F35" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G35" s="25">
+        <v>0</v>
+      </c>
+      <c r="H35" s="25">
+        <v>4</v>
+      </c>
+      <c r="I35" s="25">
+        <v>7</v>
+      </c>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="45"/>
+      <c r="M35" s="45"/>
+      <c r="N35" s="45"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+    </row>
+    <row r="36" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B36" s="25">
+        <v>8</v>
+      </c>
+      <c r="C36" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="D36" s="25">
+        <v>50</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="F36" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G36" s="25">
+        <v>0</v>
+      </c>
+      <c r="H36" s="25">
+        <v>4</v>
+      </c>
+      <c r="I36" s="25">
+        <v>8</v>
+      </c>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B37" s="25">
+        <v>9</v>
+      </c>
+      <c r="C37" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="D37" s="25">
+        <v>50</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="F37" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G37" s="25">
+        <v>0</v>
+      </c>
+      <c r="H37" s="25">
+        <v>4</v>
+      </c>
+      <c r="I37" s="25">
+        <v>1</v>
+      </c>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="45"/>
+      <c r="M37" s="45"/>
+      <c r="N37" s="45"/>
+      <c r="P37" s="19"/>
+    </row>
+    <row r="38" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B38" s="25">
+        <v>10</v>
+      </c>
+      <c r="C38" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="D38" s="25">
+        <v>20</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="F38" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G38" s="25">
+        <v>0</v>
+      </c>
+      <c r="H38" s="25">
+        <v>4</v>
+      </c>
+      <c r="I38" s="25">
+        <v>2</v>
+      </c>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="45"/>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B39" s="25">
+        <v>11</v>
+      </c>
+      <c r="C39" s="72" t="s">
+        <v>532</v>
+      </c>
+      <c r="D39" s="25">
+        <v>30</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="F39" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G39" s="25">
+        <v>0</v>
+      </c>
+      <c r="H39" s="25">
+        <v>3</v>
+      </c>
+      <c r="I39" s="25">
+        <v>9</v>
+      </c>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="45"/>
+      <c r="M39" s="45"/>
+      <c r="N39" s="45"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B40" s="25">
+        <v>12</v>
+      </c>
+      <c r="C40" s="72" t="s">
+        <v>534</v>
+      </c>
+      <c r="D40" s="25">
+        <v>20</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="F40" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G40" s="25">
+        <v>0</v>
+      </c>
+      <c r="H40" s="25">
+        <v>3</v>
+      </c>
+      <c r="I40" s="25">
+        <v>10</v>
+      </c>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="45"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B41" s="25">
+        <v>13</v>
+      </c>
+      <c r="C41" s="72" t="s">
+        <v>536</v>
+      </c>
+      <c r="D41" s="25">
+        <v>40</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="F41" s="25">
+        <v>258369741</v>
+      </c>
+      <c r="G41" s="25">
+        <v>0</v>
+      </c>
+      <c r="H41" s="25">
+        <v>1</v>
+      </c>
+      <c r="I41" s="25">
+        <v>5</v>
+      </c>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
+      <c r="M41" s="45"/>
+      <c r="N41" s="45"/>
+      <c r="AA41" s="46"/>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="45"/>
+      <c r="AA42" s="42"/>
+      <c r="AB42" s="42"/>
+      <c r="AC42" s="42"/>
+      <c r="AD42" s="42"/>
+      <c r="AE42" s="42"/>
+      <c r="AF42" s="42"/>
+      <c r="AG42" s="42"/>
+      <c r="AH42" s="42"/>
+    </row>
+    <row r="43" spans="2:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="68" t="s">
+        <v>538</v>
+      </c>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="45"/>
+      <c r="M43" s="45"/>
+      <c r="N43" s="45"/>
+    </row>
+    <row r="44" spans="2:35" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="69" t="s">
+        <v>539</v>
+      </c>
+      <c r="C44" s="70" t="s">
+        <v>540</v>
+      </c>
+      <c r="D44" s="70" t="s">
+        <v>541</v>
+      </c>
+      <c r="E44" s="70" t="s">
+        <v>542</v>
+      </c>
+      <c r="F44" s="70" t="s">
+        <v>543</v>
+      </c>
+      <c r="G44" s="76" t="s">
+        <v>544</v>
+      </c>
+      <c r="H44" s="77" t="s">
+        <v>545</v>
+      </c>
+      <c r="I44" s="78"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="45"/>
+      <c r="M44" s="45"/>
+      <c r="N44" s="45"/>
+      <c r="O44" s="5"/>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B45" s="25">
+        <v>1</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>546</v>
+      </c>
+      <c r="D45" s="72" t="s">
+        <v>547</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="F45" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G45" s="25" t="s">
+        <v>548</v>
+      </c>
+      <c r="H45" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I45" s="45"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="45"/>
+      <c r="M45" s="45"/>
+      <c r="N45" s="45"/>
+      <c r="O45" s="45"/>
+      <c r="P45" s="45"/>
+      <c r="Q45" s="45"/>
+      <c r="R45" s="45"/>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B46" s="25">
+        <v>2</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>551</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="F46" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G46" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="H46" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="45"/>
+      <c r="M46" s="45"/>
+      <c r="N46" s="45"/>
+      <c r="O46" s="45"/>
+      <c r="P46" s="45"/>
+      <c r="Q46" s="80"/>
+      <c r="R46" s="80"/>
+      <c r="T46" s="45"/>
+      <c r="U46" s="45"/>
+      <c r="V46" s="45"/>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B47" s="25">
+        <v>3</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="F47" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G47" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="H47" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="45"/>
+      <c r="M47" s="45"/>
+      <c r="N47" s="45"/>
+      <c r="O47" s="45"/>
+      <c r="P47" s="45"/>
+      <c r="Q47" s="80"/>
+      <c r="R47" s="80"/>
+      <c r="T47" s="45"/>
+      <c r="U47" s="45"/>
+      <c r="V47" s="45"/>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.25">
+      <c r="B48" s="25">
+        <v>4</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>557</v>
+      </c>
+      <c r="E48" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="F48" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G48" s="25" t="s">
+        <v>558</v>
+      </c>
+      <c r="H48" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
+      <c r="M48" s="45"/>
+      <c r="N48" s="45"/>
+      <c r="O48" s="45"/>
+      <c r="P48" s="45"/>
+      <c r="Q48" s="80"/>
+      <c r="R48" s="80"/>
+      <c r="T48" s="45"/>
+      <c r="U48" s="45"/>
+      <c r="V48" s="45"/>
+      <c r="AE48" s="73"/>
+      <c r="AF48" s="73"/>
+    </row>
+    <row r="49" spans="2:32" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="25">
+        <v>5</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>559</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>560</v>
+      </c>
+      <c r="E49" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="F49" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G49" s="25" t="s">
+        <v>561</v>
+      </c>
+      <c r="H49" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="45"/>
+      <c r="M49" s="45"/>
+      <c r="N49" s="45"/>
+      <c r="O49" s="45"/>
+      <c r="P49" s="45"/>
+      <c r="Q49" s="80"/>
+      <c r="R49" s="80"/>
+      <c r="T49" s="45"/>
+      <c r="U49" s="45"/>
+      <c r="V49" s="45"/>
+      <c r="AE49" s="73"/>
+      <c r="AF49" s="73"/>
+    </row>
+    <row r="50" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B50" s="25">
+        <v>6</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>562</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="E50" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="F50" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G50" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="H50" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
+      <c r="M50" s="45"/>
+      <c r="N50" s="45"/>
+      <c r="O50" s="45"/>
+      <c r="P50" s="45"/>
+      <c r="Q50" s="80"/>
+      <c r="R50" s="80"/>
+      <c r="AE50" s="73"/>
+      <c r="AF50" s="73"/>
+    </row>
+    <row r="51" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B51" s="25">
+        <v>7</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>566</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="F51" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G51" s="25" t="s">
+        <v>567</v>
+      </c>
+      <c r="H51" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I51" s="45"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="45"/>
+      <c r="M51" s="45"/>
+      <c r="N51" s="45"/>
+      <c r="O51" s="45"/>
+      <c r="P51" s="45"/>
+      <c r="Q51" s="80"/>
+      <c r="R51" s="80"/>
+      <c r="AE51" s="73"/>
+      <c r="AF51" s="73"/>
+    </row>
+    <row r="52" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B52" s="25">
+        <v>8</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>568</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="F52" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G52" s="25" t="s">
+        <v>570</v>
+      </c>
+      <c r="H52" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I52" s="45"/>
+      <c r="J52" s="45"/>
+      <c r="K52" s="45"/>
+      <c r="L52" s="45"/>
+      <c r="M52" s="45"/>
+      <c r="N52" s="45"/>
+      <c r="O52" s="45"/>
+      <c r="P52" s="45"/>
+      <c r="Q52" s="80"/>
+      <c r="R52" s="80"/>
+      <c r="AE52" s="73"/>
+      <c r="AF52" s="73"/>
+    </row>
+    <row r="53" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B53" s="25">
+        <v>9</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>571</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="F53" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G53" s="25" t="s">
+        <v>573</v>
+      </c>
+      <c r="H53" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I53" s="45"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="45"/>
+      <c r="M53" s="45"/>
+      <c r="N53" s="45"/>
+      <c r="O53" s="45"/>
+      <c r="P53" s="45"/>
+      <c r="Q53" s="80"/>
+      <c r="R53" s="80"/>
+    </row>
+    <row r="54" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B54" s="25">
+        <v>10</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>574</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>575</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="F54" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G54" s="25" t="s">
+        <v>576</v>
+      </c>
+      <c r="H54" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I54" s="45"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="45"/>
+      <c r="M54" s="45"/>
+      <c r="N54" s="45"/>
+      <c r="O54" s="45"/>
+      <c r="P54" s="45"/>
+      <c r="Q54" s="80"/>
+      <c r="R54" s="80"/>
+    </row>
+    <row r="55" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B55" s="45"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="45"/>
+      <c r="H55" s="45"/>
+      <c r="I55" s="45"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="45"/>
+      <c r="L55" s="45"/>
+      <c r="M55" s="45"/>
+      <c r="N55" s="45"/>
+      <c r="O55" s="45"/>
+      <c r="P55" s="45"/>
+      <c r="Q55" s="80"/>
+      <c r="R55" s="80"/>
+    </row>
+    <row r="56" spans="2:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B56" s="68" t="s">
+        <v>577</v>
+      </c>
+      <c r="C56" s="45"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
+      <c r="J56" s="45"/>
+      <c r="K56" s="45"/>
+      <c r="L56" s="45"/>
+      <c r="M56" s="45"/>
+      <c r="N56" s="45"/>
+      <c r="O56" s="45"/>
+      <c r="P56" s="45"/>
+      <c r="Q56" s="80"/>
+      <c r="R56" s="80"/>
+    </row>
+    <row r="57" spans="2:32" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="69" t="s">
+        <v>578</v>
+      </c>
+      <c r="C57" s="70" t="s">
+        <v>579</v>
+      </c>
+      <c r="D57" s="70" t="s">
+        <v>580</v>
+      </c>
+      <c r="E57" s="70" t="s">
+        <v>581</v>
+      </c>
+      <c r="F57" s="70" t="s">
+        <v>582</v>
+      </c>
+      <c r="G57" s="70" t="s">
+        <v>583</v>
+      </c>
+      <c r="H57" s="70" t="s">
+        <v>584</v>
+      </c>
+      <c r="I57" s="71" t="s">
+        <v>585</v>
+      </c>
+      <c r="J57" s="45"/>
+      <c r="K57" s="45"/>
+      <c r="L57" s="45"/>
+      <c r="M57" s="45"/>
+      <c r="N57" s="45"/>
+      <c r="O57" s="45"/>
+      <c r="P57" s="45"/>
+      <c r="Q57" s="80"/>
+      <c r="R57" s="80"/>
+    </row>
+    <row r="58" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B58" s="25">
+        <v>1</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>586</v>
+      </c>
+      <c r="D58" s="72" t="s">
+        <v>587</v>
+      </c>
+      <c r="E58" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="F58" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G58" s="25" t="s">
+        <v>588</v>
+      </c>
+      <c r="H58" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I58" s="25">
+        <v>1</v>
+      </c>
+      <c r="J58" s="45"/>
+      <c r="K58" s="45"/>
+      <c r="L58" s="45"/>
+      <c r="M58" s="45"/>
+      <c r="N58" s="45"/>
+      <c r="O58" s="45"/>
+      <c r="P58" s="45"/>
+      <c r="Q58" s="80"/>
+      <c r="R58" s="80"/>
+    </row>
+    <row r="59" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B59" s="25">
+        <v>2</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>589</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>590</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="F59" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G59" s="25" t="s">
+        <v>591</v>
+      </c>
+      <c r="H59" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I59" s="25">
+        <v>1</v>
+      </c>
+      <c r="J59" s="45"/>
+      <c r="K59" s="45"/>
+      <c r="L59" s="45"/>
+      <c r="M59" s="45"/>
+      <c r="N59" s="45"/>
+      <c r="O59" s="45"/>
+      <c r="P59" s="45"/>
+      <c r="Q59" s="80"/>
+      <c r="R59" s="80"/>
+    </row>
+    <row r="60" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B60" s="25">
+        <v>3</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>592</v>
+      </c>
+      <c r="D60" s="72" t="s">
+        <v>593</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="F60" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G60" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="H60" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I60" s="25">
+        <v>2</v>
+      </c>
+      <c r="J60" s="45"/>
+      <c r="K60" s="45"/>
+      <c r="L60" s="45"/>
+      <c r="M60" s="45"/>
+      <c r="N60" s="45"/>
+      <c r="O60" s="45"/>
+      <c r="P60" s="45"/>
+      <c r="Q60" s="80"/>
+      <c r="R60" s="80"/>
+    </row>
+    <row r="61" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B61" s="25">
+        <v>4</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>595</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>596</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="F61" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G61" s="25" t="s">
+        <v>597</v>
+      </c>
+      <c r="H61" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I61" s="25">
+        <v>1</v>
+      </c>
+      <c r="J61" s="45"/>
+      <c r="K61" s="45"/>
+      <c r="L61" s="45"/>
+      <c r="M61" s="45"/>
+      <c r="N61" s="45"/>
+      <c r="O61" s="45"/>
+      <c r="P61" s="45"/>
+      <c r="Q61" s="80"/>
+      <c r="R61" s="80"/>
+    </row>
+    <row r="62" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B62" s="25">
+        <v>5</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>598</v>
+      </c>
+      <c r="D62" s="72" t="s">
+        <v>599</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="F62" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G62" s="25" t="s">
+        <v>600</v>
+      </c>
+      <c r="H62" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I62" s="25">
+        <v>1</v>
+      </c>
+      <c r="J62" s="45"/>
+      <c r="K62" s="45"/>
+      <c r="L62" s="45"/>
+      <c r="M62" s="45"/>
+      <c r="N62" s="45"/>
+    </row>
+    <row r="63" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B63" s="25">
+        <v>6</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>601</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>602</v>
+      </c>
+      <c r="E63" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="F63" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G63" s="25" t="s">
+        <v>603</v>
+      </c>
+      <c r="H63" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I63" s="25">
+        <v>1</v>
+      </c>
+      <c r="J63" s="45"/>
+      <c r="K63" s="45"/>
+      <c r="L63" s="45"/>
+      <c r="M63" s="45"/>
+      <c r="N63" s="45"/>
+    </row>
+    <row r="64" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B64" s="25">
+        <v>7</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>604</v>
+      </c>
+      <c r="D64" s="72" t="s">
+        <v>605</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="F64" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G64" s="25" t="s">
+        <v>606</v>
+      </c>
+      <c r="H64" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I64" s="25">
+        <v>2</v>
+      </c>
+      <c r="J64" s="45"/>
+      <c r="K64" s="45"/>
+      <c r="L64" s="45"/>
+      <c r="M64" s="45"/>
+      <c r="N64" s="45"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B65" s="25">
+        <v>8</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>607</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>608</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="F65" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G65" s="25" t="s">
+        <v>609</v>
+      </c>
+      <c r="H65" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I65" s="25">
+        <v>3</v>
+      </c>
+      <c r="J65" s="45"/>
+      <c r="K65" s="45"/>
+      <c r="L65" s="45"/>
+      <c r="M65" s="45"/>
+      <c r="N65" s="45"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B66" s="25">
+        <v>9</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>610</v>
+      </c>
+      <c r="D66" s="72" t="s">
+        <v>611</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="F66" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G66" s="25" t="s">
+        <v>612</v>
+      </c>
+      <c r="H66" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I66" s="25">
+        <v>1</v>
+      </c>
+      <c r="J66" s="45"/>
+      <c r="K66" s="45"/>
+      <c r="L66" s="45"/>
+      <c r="M66" s="45"/>
+      <c r="N66" s="45"/>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B67" s="25">
+        <v>10</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>613</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>614</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="F67" s="25">
+        <v>123456789</v>
+      </c>
+      <c r="G67" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="H67" s="79" t="s">
+        <v>549</v>
+      </c>
+      <c r="I67" s="25">
+        <v>4</v>
+      </c>
+      <c r="J67" s="45"/>
+      <c r="K67" s="45"/>
+      <c r="L67" s="45"/>
+      <c r="M67" s="45"/>
+      <c r="N67" s="45"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B68" s="45"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="45"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="45"/>
+      <c r="G68" s="45"/>
+      <c r="H68" s="45"/>
+      <c r="I68" s="45"/>
+      <c r="J68" s="45"/>
+      <c r="K68" s="45"/>
+      <c r="L68" s="45"/>
+      <c r="M68" s="45"/>
+      <c r="N68" s="45"/>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B69" s="45"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="45"/>
+      <c r="H69" s="45"/>
+      <c r="I69" s="45"/>
+      <c r="J69" s="45"/>
+      <c r="K69" s="45"/>
+      <c r="L69" s="45"/>
+      <c r="M69" s="45"/>
+      <c r="N69" s="45"/>
+    </row>
+    <row r="70" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B70" s="81" t="s">
+        <v>616</v>
+      </c>
+      <c r="C70" s="45"/>
+      <c r="D70" s="45"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="45"/>
+      <c r="H70" s="45"/>
+      <c r="I70" s="45"/>
+      <c r="J70" s="45"/>
+      <c r="K70" s="45"/>
+      <c r="L70" s="45"/>
+      <c r="M70" s="45"/>
+      <c r="N70" s="45"/>
+    </row>
+    <row r="71" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B71" s="69" t="s">
+        <v>617</v>
+      </c>
+      <c r="C71" s="82" t="s">
+        <v>618</v>
+      </c>
+      <c r="D71" s="82" t="s">
+        <v>619</v>
+      </c>
+      <c r="E71" s="70" t="s">
+        <v>620</v>
+      </c>
+      <c r="F71" s="70" t="s">
+        <v>621</v>
+      </c>
+      <c r="G71" s="45"/>
+      <c r="H71" s="45"/>
+      <c r="I71" s="45"/>
+      <c r="J71" s="45"/>
+      <c r="K71" s="45"/>
+      <c r="L71" s="45"/>
+      <c r="M71" s="45"/>
+      <c r="N71" s="45"/>
+      <c r="Q71" s="5"/>
+      <c r="W71" s="19"/>
+      <c r="X71" s="19"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="45"/>
+      <c r="C72" s="45"/>
+      <c r="D72" s="45"/>
+      <c r="E72" s="45"/>
+      <c r="F72" s="45"/>
+      <c r="G72" s="45"/>
+      <c r="H72" s="45"/>
+      <c r="I72" s="45"/>
+      <c r="J72" s="45"/>
+      <c r="K72" s="45"/>
+      <c r="L72" s="45"/>
+      <c r="M72" s="45"/>
+      <c r="N72" s="45"/>
+      <c r="Q72" s="5"/>
+      <c r="R72" s="5"/>
+      <c r="W72" s="5"/>
+      <c r="X72" s="5"/>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B73" s="45"/>
+      <c r="C73" s="93" t="s">
+        <v>622</v>
+      </c>
+      <c r="D73" s="93"/>
+      <c r="E73" s="93"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="45"/>
+      <c r="H73" s="45"/>
+      <c r="I73" s="45"/>
+      <c r="J73" s="45"/>
+      <c r="K73" s="45"/>
+      <c r="L73" s="45"/>
+      <c r="M73" s="45"/>
+      <c r="N73" s="45"/>
+      <c r="Q73" s="5"/>
+      <c r="R73" s="5"/>
+      <c r="W73" s="5"/>
+      <c r="X73" s="5"/>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="45"/>
+      <c r="C74" s="93"/>
+      <c r="D74" s="93"/>
+      <c r="E74" s="93"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
+      <c r="H74" s="45"/>
+      <c r="I74" s="45"/>
+      <c r="J74" s="45"/>
+      <c r="K74" s="45"/>
+      <c r="L74" s="45"/>
+      <c r="M74" s="45"/>
+      <c r="N74" s="45"/>
+      <c r="Q74" s="5"/>
+      <c r="R74" s="5"/>
+      <c r="W74" s="5"/>
+      <c r="X74" s="5"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="45"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="45"/>
+      <c r="J75" s="45"/>
+      <c r="K75" s="45"/>
+      <c r="L75" s="45"/>
+      <c r="M75" s="45"/>
+      <c r="N75" s="45"/>
+      <c r="Q75" s="5"/>
+      <c r="R75" s="5"/>
+      <c r="W75" s="5"/>
+      <c r="X75" s="5"/>
+    </row>
+    <row r="76" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B76" s="81" t="s">
+        <v>623</v>
+      </c>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="45"/>
+      <c r="H76" s="45"/>
+      <c r="I76" s="45"/>
+      <c r="J76" s="45"/>
+      <c r="K76" s="45"/>
+      <c r="L76" s="45"/>
+      <c r="M76" s="45"/>
+      <c r="N76" s="45"/>
+      <c r="Q76" s="5"/>
+      <c r="R76" s="5"/>
+    </row>
+    <row r="77" spans="2:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B77" s="69" t="s">
+        <v>624</v>
+      </c>
+      <c r="C77" s="69" t="s">
+        <v>625</v>
+      </c>
+      <c r="D77" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E77" s="70" t="s">
+        <v>627</v>
+      </c>
+      <c r="F77" s="45"/>
+      <c r="G77" s="45"/>
+      <c r="H77" s="45"/>
+      <c r="I77" s="45"/>
+      <c r="J77" s="45"/>
+      <c r="K77" s="45"/>
+      <c r="L77" s="45"/>
+      <c r="M77" s="45"/>
+      <c r="N77" s="45"/>
+      <c r="Q77" s="5"/>
+      <c r="R77" s="5"/>
+    </row>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="45"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="45"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="45"/>
+      <c r="H78" s="45"/>
+      <c r="I78" s="45"/>
+      <c r="J78" s="45"/>
+      <c r="K78" s="45"/>
+      <c r="L78" s="45"/>
+      <c r="M78" s="45"/>
+      <c r="N78" s="45"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="45"/>
+      <c r="C79" s="93" t="s">
+        <v>622</v>
+      </c>
+      <c r="D79" s="93"/>
+      <c r="E79" s="45"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="45"/>
+      <c r="H79" s="45"/>
+      <c r="I79" s="45"/>
+      <c r="J79" s="45"/>
+      <c r="K79" s="45"/>
+      <c r="L79" s="45"/>
+      <c r="M79" s="45"/>
+      <c r="N79" s="45"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="45"/>
+      <c r="C80" s="93"/>
+      <c r="D80" s="93"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45"/>
+      <c r="I80" s="45"/>
+      <c r="J80" s="45"/>
+      <c r="K80" s="45"/>
+      <c r="L80" s="45"/>
+      <c r="M80" s="45"/>
+      <c r="N80" s="45"/>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B81" s="45"/>
+      <c r="C81" s="45"/>
+      <c r="D81" s="45"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="45"/>
+      <c r="G81" s="45"/>
+      <c r="H81" s="45"/>
+      <c r="I81" s="45"/>
+      <c r="J81" s="45"/>
+      <c r="K81" s="45"/>
+      <c r="L81" s="45"/>
+      <c r="M81" s="45"/>
+      <c r="N81" s="45"/>
+    </row>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B82" s="45"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="45"/>
+      <c r="J82" s="45"/>
+      <c r="K82" s="45"/>
+      <c r="L82" s="45"/>
+      <c r="M82" s="45"/>
+      <c r="N82" s="45"/>
+    </row>
+    <row r="83" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B83" s="68" t="s">
+        <v>628</v>
+      </c>
+      <c r="C83" s="45"/>
+      <c r="D83" s="45"/>
+      <c r="E83" s="45"/>
+      <c r="F83" s="45"/>
+      <c r="G83" s="45"/>
+      <c r="H83" s="45"/>
+      <c r="I83" s="45"/>
+      <c r="J83" s="45"/>
+      <c r="K83" s="45"/>
+      <c r="L83" s="45"/>
+      <c r="M83" s="45"/>
+      <c r="N83" s="45"/>
+    </row>
+    <row r="84" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B84" s="69" t="s">
+        <v>629</v>
+      </c>
+      <c r="C84" s="76" t="s">
+        <v>630</v>
+      </c>
+      <c r="D84" s="76" t="s">
+        <v>631</v>
+      </c>
+      <c r="E84" s="76" t="s">
+        <v>632</v>
+      </c>
+      <c r="F84" s="70" t="s">
+        <v>633</v>
+      </c>
+      <c r="G84" s="70" t="s">
+        <v>634</v>
+      </c>
+      <c r="H84" s="45"/>
+      <c r="I84" s="45"/>
+      <c r="J84" s="45"/>
+      <c r="K84" s="45"/>
+      <c r="L84" s="45"/>
+      <c r="M84" s="45"/>
+      <c r="N84" s="45"/>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B85" s="45" t="s">
+        <v>635</v>
+      </c>
+      <c r="C85" s="45"/>
+      <c r="D85" s="45"/>
+      <c r="E85" s="45"/>
+      <c r="F85" s="45"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
+      <c r="I85" s="45"/>
+      <c r="J85" s="45"/>
+      <c r="K85" s="45"/>
+      <c r="L85" s="45"/>
+      <c r="M85" s="45"/>
+      <c r="N85" s="45"/>
+    </row>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B86" s="45"/>
+      <c r="C86" s="94" t="s">
+        <v>636</v>
+      </c>
+      <c r="D86" s="93"/>
+      <c r="E86" s="93"/>
+      <c r="F86" s="93"/>
+      <c r="G86" s="45"/>
+      <c r="H86" s="45"/>
+      <c r="I86" s="45"/>
+      <c r="J86" s="45"/>
+      <c r="K86" s="45"/>
+      <c r="L86" s="45"/>
+      <c r="M86" s="45"/>
+      <c r="N86" s="45"/>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B87" s="45"/>
+      <c r="C87" s="93"/>
+      <c r="D87" s="93"/>
+      <c r="E87" s="93"/>
+      <c r="F87" s="93"/>
+      <c r="G87" s="45"/>
+      <c r="H87" s="45"/>
+      <c r="I87" s="45"/>
+      <c r="J87" s="45"/>
+      <c r="K87" s="45"/>
+      <c r="L87" s="45"/>
+      <c r="M87" s="45"/>
+      <c r="N87" s="45"/>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B88" s="45"/>
+      <c r="C88" s="93"/>
+      <c r="D88" s="93"/>
+      <c r="E88" s="93"/>
+      <c r="F88" s="93"/>
+      <c r="G88" s="45"/>
+      <c r="H88" s="45"/>
+      <c r="I88" s="45"/>
+      <c r="J88" s="45"/>
+      <c r="K88" s="45"/>
+      <c r="L88" s="45"/>
+      <c r="M88" s="45"/>
+      <c r="N88" s="45"/>
+    </row>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B89" s="45"/>
+      <c r="C89" s="93"/>
+      <c r="D89" s="93"/>
+      <c r="E89" s="93"/>
+      <c r="F89" s="93"/>
+      <c r="G89" s="45"/>
+      <c r="H89" s="45"/>
+      <c r="I89" s="45"/>
+      <c r="J89" s="45"/>
+      <c r="K89" s="45"/>
+      <c r="L89" s="45"/>
+      <c r="M89" s="45"/>
+      <c r="N89" s="45"/>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B90" s="45"/>
+      <c r="C90" s="45"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="45"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="45"/>
+      <c r="J90" s="45"/>
+      <c r="K90" s="45"/>
+      <c r="L90" s="45"/>
+      <c r="M90" s="45"/>
+      <c r="N90" s="45"/>
+    </row>
+    <row r="91" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B91" s="68" t="s">
+        <v>637</v>
+      </c>
+      <c r="C91" s="45"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="45"/>
+      <c r="H91" s="45"/>
+      <c r="I91" s="45"/>
+      <c r="J91" s="45"/>
+      <c r="K91" s="45"/>
+      <c r="L91" s="45"/>
+      <c r="M91" s="45"/>
+      <c r="N91" s="45"/>
+    </row>
+    <row r="92" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="69" t="s">
+        <v>638</v>
+      </c>
+      <c r="C92" s="71" t="s">
+        <v>639</v>
+      </c>
+      <c r="D92" s="45"/>
+      <c r="E92" s="45"/>
+      <c r="F92" s="45"/>
+      <c r="G92" s="45"/>
+      <c r="H92" s="45"/>
+      <c r="I92" s="45"/>
+      <c r="J92" s="45"/>
+      <c r="K92" s="45"/>
+      <c r="L92" s="45"/>
+      <c r="M92" s="45"/>
+      <c r="N92" s="45"/>
+    </row>
+    <row r="93" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B93" s="101" t="s">
+        <v>640</v>
+      </c>
+      <c r="C93" s="101"/>
+      <c r="D93" s="45"/>
+      <c r="E93" s="45"/>
+      <c r="F93" s="45"/>
+      <c r="G93" s="45"/>
+      <c r="H93" s="45"/>
+      <c r="I93" s="45"/>
+      <c r="J93" s="45"/>
+      <c r="K93" s="45"/>
+      <c r="L93" s="45"/>
+      <c r="M93" s="45"/>
+      <c r="N93" s="45"/>
+    </row>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B94" s="93"/>
+      <c r="C94" s="93"/>
+      <c r="D94" s="45"/>
+      <c r="E94" s="45"/>
+      <c r="F94" s="45"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="45"/>
+      <c r="I94" s="45"/>
+      <c r="J94" s="45"/>
+      <c r="K94" s="45"/>
+      <c r="L94" s="45"/>
+      <c r="M94" s="45"/>
+      <c r="N94" s="45"/>
+    </row>
+    <row r="95" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B95" s="93"/>
+      <c r="C95" s="93"/>
+      <c r="D95" s="45"/>
+      <c r="E95" s="45"/>
+      <c r="F95" s="45"/>
+      <c r="G95" s="45"/>
+      <c r="H95" s="45"/>
+      <c r="I95" s="45"/>
+      <c r="J95" s="45"/>
+      <c r="K95" s="45"/>
+      <c r="L95" s="45"/>
+      <c r="M95" s="45"/>
+      <c r="N95" s="45"/>
+    </row>
+    <row r="96" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B96" s="45"/>
+      <c r="C96" s="45"/>
+      <c r="D96" s="45"/>
+      <c r="E96" s="45"/>
+      <c r="F96" s="45"/>
+      <c r="G96" s="45"/>
+      <c r="H96" s="45"/>
+      <c r="I96" s="45"/>
+      <c r="J96" s="45"/>
+      <c r="K96" s="45"/>
+      <c r="L96" s="45"/>
+      <c r="M96" s="45"/>
+      <c r="N96" s="45"/>
+    </row>
+    <row r="97" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="68" t="s">
+        <v>641</v>
+      </c>
+      <c r="C97" s="45"/>
+      <c r="D97" s="45"/>
+      <c r="E97" s="45"/>
+      <c r="F97" s="45"/>
+      <c r="G97" s="45"/>
+      <c r="H97" s="45"/>
+      <c r="I97" s="45"/>
+      <c r="J97" s="45"/>
+      <c r="K97" s="45"/>
+      <c r="L97" s="45"/>
+      <c r="M97" s="45"/>
+      <c r="N97" s="45"/>
+    </row>
+    <row r="98" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B98" s="69" t="s">
+        <v>642</v>
+      </c>
+      <c r="C98" s="69" t="s">
+        <v>643</v>
+      </c>
+      <c r="D98" s="70" t="s">
+        <v>644</v>
+      </c>
+      <c r="E98" s="45"/>
+      <c r="F98" s="68" t="s">
+        <v>645</v>
+      </c>
+      <c r="G98" s="45"/>
+      <c r="H98" s="45"/>
+      <c r="I98" s="45"/>
+      <c r="J98" s="45"/>
+      <c r="K98" s="45"/>
+      <c r="L98" s="45"/>
+      <c r="M98" s="45"/>
+      <c r="N98" s="45"/>
+    </row>
+    <row r="99" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B99" s="99" t="s">
+        <v>646</v>
+      </c>
+      <c r="C99" s="99"/>
+      <c r="D99" s="99"/>
+      <c r="E99" s="45"/>
+      <c r="F99" s="69" t="s">
+        <v>338</v>
+      </c>
+      <c r="G99" s="69" t="s">
+        <v>647</v>
+      </c>
+      <c r="H99" s="71" t="s">
+        <v>648</v>
+      </c>
+      <c r="I99" s="70" t="s">
+        <v>649</v>
+      </c>
+      <c r="J99" s="45"/>
+      <c r="K99" s="45"/>
+      <c r="L99" s="45"/>
+      <c r="M99" s="45"/>
+      <c r="N99" s="45"/>
+    </row>
+    <row r="100" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B100" s="99"/>
+      <c r="C100" s="99"/>
+      <c r="D100" s="99"/>
+      <c r="E100" s="45"/>
+      <c r="F100" s="25"/>
+      <c r="G100" s="25"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="45"/>
+      <c r="K100" s="45"/>
+      <c r="L100" s="45"/>
+      <c r="M100" s="45"/>
+      <c r="N100" s="45"/>
+    </row>
+    <row r="101" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B101" s="99"/>
+      <c r="C101" s="99"/>
+      <c r="D101" s="99"/>
+      <c r="E101" s="45"/>
+      <c r="F101" s="83" t="s">
+        <v>650</v>
+      </c>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25" t="s">
+        <v>586</v>
+      </c>
+      <c r="I101" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="J101" s="45"/>
+      <c r="K101" s="45"/>
+      <c r="L101" s="45"/>
+      <c r="M101" s="45"/>
+      <c r="N101" s="45"/>
+    </row>
+    <row r="102" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B102" s="25">
+        <v>1</v>
+      </c>
+      <c r="C102" s="25">
+        <v>1</v>
+      </c>
+      <c r="D102" s="25">
+        <v>2</v>
+      </c>
+      <c r="E102" s="45"/>
+      <c r="F102" s="83" t="s">
+        <v>652</v>
+      </c>
+      <c r="G102" s="25"/>
+      <c r="H102" s="25" t="s">
+        <v>653</v>
+      </c>
+      <c r="I102" s="72" t="s">
+        <v>654</v>
+      </c>
+      <c r="J102" s="45"/>
+      <c r="K102" s="45"/>
+      <c r="L102" s="45"/>
+      <c r="M102" s="45"/>
+      <c r="N102" s="45"/>
+    </row>
+    <row r="103" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B103" s="25">
+        <v>1</v>
+      </c>
+      <c r="C103" s="25">
+        <v>3</v>
+      </c>
+      <c r="D103" s="25">
+        <v>4</v>
+      </c>
+      <c r="E103" s="45"/>
+      <c r="F103" s="83" t="s">
+        <v>655</v>
+      </c>
+      <c r="G103" s="25"/>
+      <c r="H103" s="25" t="s">
+        <v>656</v>
+      </c>
+      <c r="I103" s="72" t="s">
+        <v>654</v>
+      </c>
+      <c r="J103" s="45"/>
+      <c r="K103" s="45"/>
+      <c r="L103" s="45"/>
+      <c r="M103" s="45"/>
+      <c r="N103" s="45"/>
+    </row>
+    <row r="104" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B104" s="25">
+        <v>2</v>
+      </c>
+      <c r="C104" s="25">
+        <v>4</v>
+      </c>
+      <c r="D104" s="25">
+        <v>2</v>
+      </c>
+      <c r="E104" s="45"/>
+      <c r="F104" s="83" t="s">
+        <v>657</v>
+      </c>
+      <c r="G104" s="25"/>
+      <c r="H104" s="25" t="s">
+        <v>658</v>
+      </c>
+      <c r="I104" s="72" t="s">
+        <v>654</v>
+      </c>
+      <c r="J104" s="45"/>
+      <c r="K104" s="45"/>
+      <c r="L104" s="45"/>
+      <c r="M104" s="45"/>
+      <c r="N104" s="45"/>
+    </row>
+    <row r="105" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B105" s="25">
+        <v>2</v>
+      </c>
+      <c r="C105" s="25">
+        <v>5</v>
+      </c>
+      <c r="D105" s="25">
+        <v>2</v>
+      </c>
+      <c r="E105" s="45"/>
+      <c r="F105" s="83" t="s">
+        <v>659</v>
+      </c>
+      <c r="G105" s="25"/>
+      <c r="H105" s="25" t="s">
+        <v>660</v>
+      </c>
+      <c r="I105" s="25"/>
+      <c r="J105" s="45"/>
+      <c r="K105" s="45"/>
+      <c r="L105" s="45"/>
+      <c r="M105" s="45"/>
+      <c r="N105" s="45"/>
+    </row>
+    <row r="106" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B106" s="25">
+        <v>3</v>
+      </c>
+      <c r="C106" s="25">
+        <v>6</v>
+      </c>
+      <c r="D106" s="25">
+        <v>4</v>
+      </c>
+      <c r="E106" s="45"/>
+      <c r="F106" s="25"/>
+      <c r="G106" s="25"/>
+      <c r="H106" s="25"/>
+      <c r="I106" s="25"/>
+      <c r="J106" s="45"/>
+      <c r="K106" s="45"/>
+      <c r="L106" s="45"/>
+      <c r="M106" s="45"/>
+      <c r="N106" s="45"/>
+    </row>
+    <row r="107" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B107" s="25">
+        <v>3</v>
+      </c>
+      <c r="C107" s="25">
+        <v>2</v>
+      </c>
+      <c r="D107" s="25">
+        <v>4</v>
+      </c>
+      <c r="E107" s="45"/>
+      <c r="F107" s="45"/>
+      <c r="G107" s="45"/>
+      <c r="H107" s="45"/>
+      <c r="I107" s="45"/>
+      <c r="J107" s="45"/>
+      <c r="K107" s="45"/>
+      <c r="L107" s="45"/>
+      <c r="M107" s="45"/>
+      <c r="N107" s="45"/>
+    </row>
+    <row r="108" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B108" s="25">
+        <v>4</v>
+      </c>
+      <c r="C108" s="25">
+        <v>8</v>
+      </c>
+      <c r="D108" s="25">
+        <v>2</v>
+      </c>
+      <c r="E108" s="45"/>
+      <c r="F108" s="45"/>
+      <c r="G108" s="45"/>
+      <c r="H108" s="45"/>
+      <c r="I108" s="45"/>
+      <c r="J108" s="45"/>
+      <c r="K108" s="45"/>
+      <c r="L108" s="45"/>
+      <c r="M108" s="45"/>
+      <c r="N108" s="45"/>
+    </row>
+    <row r="109" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B109" s="25">
+        <v>4</v>
+      </c>
+      <c r="C109" s="25">
+        <v>12</v>
+      </c>
+      <c r="D109" s="25">
+        <v>4</v>
+      </c>
+      <c r="E109" s="45"/>
+      <c r="F109" s="45"/>
+      <c r="G109" s="45"/>
+      <c r="H109" s="45"/>
+      <c r="I109" s="45"/>
+      <c r="J109" s="45"/>
+      <c r="K109" s="45"/>
+      <c r="L109" s="45"/>
+      <c r="M109" s="45"/>
+      <c r="N109" s="45"/>
+    </row>
+    <row r="110" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B110" s="25">
+        <v>5</v>
+      </c>
+      <c r="C110" s="25">
+        <v>88</v>
+      </c>
+      <c r="D110" s="25">
+        <v>1</v>
+      </c>
+      <c r="E110" s="45"/>
+      <c r="F110" s="45"/>
+      <c r="G110" s="45"/>
+      <c r="H110" s="45"/>
+      <c r="I110" s="45"/>
+      <c r="J110" s="45"/>
+      <c r="K110" s="45"/>
+      <c r="L110" s="45"/>
+      <c r="M110" s="45"/>
+      <c r="N110" s="45"/>
+    </row>
+    <row r="111" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B111" s="25">
+        <v>5</v>
+      </c>
+      <c r="C111" s="25">
+        <v>22</v>
+      </c>
+      <c r="D111" s="25">
+        <v>3</v>
+      </c>
+      <c r="E111" s="45"/>
+      <c r="F111" s="45"/>
+      <c r="G111" s="45"/>
+      <c r="H111" s="45"/>
+      <c r="I111" s="45"/>
+      <c r="J111" s="45"/>
+      <c r="K111" s="45"/>
+      <c r="L111" s="45"/>
+      <c r="M111" s="45"/>
+      <c r="N111" s="45"/>
+    </row>
+    <row r="112" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B112" s="25">
+        <v>5</v>
+      </c>
+      <c r="C112" s="25">
+        <v>11</v>
+      </c>
+      <c r="D112" s="25">
+        <v>1</v>
+      </c>
+      <c r="E112" s="45"/>
+      <c r="F112" s="45"/>
+      <c r="G112" s="45"/>
+      <c r="H112" s="45"/>
+      <c r="I112" s="45"/>
+      <c r="J112" s="45"/>
+      <c r="K112" s="45"/>
+      <c r="L112" s="45"/>
+      <c r="M112" s="45"/>
+      <c r="N112" s="45"/>
+    </row>
+    <row r="113" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B113" s="25">
+        <v>5</v>
+      </c>
+      <c r="C113" s="25">
+        <v>33</v>
+      </c>
+      <c r="D113" s="25">
+        <v>1</v>
+      </c>
+      <c r="E113" s="45"/>
+      <c r="F113" s="45"/>
+      <c r="G113" s="45"/>
+      <c r="H113" s="45"/>
+      <c r="I113" s="45"/>
+      <c r="J113" s="45"/>
+      <c r="K113" s="45"/>
+      <c r="L113" s="45"/>
+      <c r="M113" s="45"/>
+      <c r="N113" s="45"/>
+    </row>
+    <row r="114" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B114" s="25">
+        <v>6</v>
+      </c>
+      <c r="C114" s="25">
+        <v>2</v>
+      </c>
+      <c r="D114" s="25">
+        <v>1</v>
+      </c>
+      <c r="E114" s="45"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="45"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="45"/>
+      <c r="J114" s="45"/>
+      <c r="K114" s="45"/>
+      <c r="L114" s="45"/>
+      <c r="M114" s="45"/>
+      <c r="N114" s="45"/>
+    </row>
+    <row r="115" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B115" s="25">
+        <v>7</v>
+      </c>
+      <c r="C115" s="25">
+        <v>1</v>
+      </c>
+      <c r="D115" s="25">
+        <v>2</v>
+      </c>
+      <c r="E115" s="45"/>
+      <c r="F115" s="45"/>
+      <c r="G115" s="45"/>
+      <c r="H115" s="45"/>
+      <c r="I115" s="45"/>
+      <c r="J115" s="45"/>
+      <c r="K115" s="45"/>
+      <c r="L115" s="45"/>
+      <c r="M115" s="45"/>
+      <c r="N115" s="45"/>
+    </row>
+    <row r="116" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B116" s="25">
+        <v>8</v>
+      </c>
+      <c r="C116" s="25">
+        <v>27</v>
+      </c>
+      <c r="D116" s="25">
+        <v>1</v>
+      </c>
+      <c r="E116" s="45"/>
+      <c r="F116" s="45"/>
+      <c r="G116" s="45"/>
+      <c r="H116" s="45"/>
+      <c r="I116" s="45"/>
+      <c r="J116" s="45"/>
+      <c r="K116" s="45"/>
+      <c r="L116" s="45"/>
+      <c r="M116" s="45"/>
+      <c r="N116" s="45"/>
+    </row>
+    <row r="117" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B117" s="25">
+        <v>8</v>
+      </c>
+      <c r="C117" s="25">
+        <v>23</v>
+      </c>
+      <c r="D117" s="25">
+        <v>1</v>
+      </c>
+      <c r="E117" s="45"/>
+      <c r="F117" s="45"/>
+      <c r="G117" s="45"/>
+      <c r="H117" s="45"/>
+      <c r="I117" s="45"/>
+      <c r="J117" s="45"/>
+      <c r="K117" s="45"/>
+      <c r="L117" s="45"/>
+      <c r="M117" s="45"/>
+      <c r="N117" s="45"/>
+    </row>
+    <row r="118" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B118" s="25">
+        <v>8</v>
+      </c>
+      <c r="C118" s="25">
+        <v>98</v>
+      </c>
+      <c r="D118" s="25">
+        <v>2</v>
+      </c>
+      <c r="E118" s="45"/>
+      <c r="F118" s="45"/>
+      <c r="G118" s="45"/>
+      <c r="H118" s="45"/>
+      <c r="I118" s="45"/>
+      <c r="J118" s="45"/>
+      <c r="K118" s="45"/>
+      <c r="L118" s="45"/>
+      <c r="M118" s="45"/>
+      <c r="N118" s="45"/>
+    </row>
+    <row r="119" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B119" s="25">
+        <v>9</v>
+      </c>
+      <c r="C119" s="25">
+        <v>100</v>
+      </c>
+      <c r="D119" s="25">
+        <v>6</v>
+      </c>
+      <c r="E119" s="45"/>
+      <c r="F119" s="45"/>
+      <c r="G119" s="45"/>
+      <c r="H119" s="45"/>
+      <c r="I119" s="45"/>
+      <c r="J119" s="45"/>
+      <c r="K119" s="45"/>
+      <c r="L119" s="45"/>
+      <c r="M119" s="45"/>
+      <c r="N119" s="45"/>
+    </row>
+    <row r="120" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B120" s="25">
+        <v>9</v>
+      </c>
+      <c r="C120" s="25">
+        <v>11</v>
+      </c>
+      <c r="D120" s="25">
+        <v>7</v>
+      </c>
+      <c r="E120" s="45"/>
+      <c r="F120" s="45"/>
+      <c r="G120" s="45"/>
+      <c r="H120" s="45"/>
+      <c r="I120" s="45"/>
+      <c r="J120" s="45"/>
+      <c r="K120" s="45"/>
+      <c r="L120" s="45"/>
+      <c r="M120" s="45"/>
+      <c r="N120" s="45"/>
+    </row>
+    <row r="121" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B121" s="25">
+        <v>9</v>
+      </c>
+      <c r="C121" s="25">
+        <v>45</v>
+      </c>
+      <c r="D121" s="25">
+        <v>2</v>
+      </c>
+      <c r="E121" s="45"/>
+      <c r="F121" s="45"/>
+      <c r="G121" s="45"/>
+      <c r="H121" s="45"/>
+      <c r="I121" s="45"/>
+      <c r="J121" s="45"/>
+      <c r="K121" s="45"/>
+      <c r="L121" s="45"/>
+      <c r="M121" s="45"/>
+      <c r="N121" s="45"/>
+    </row>
+    <row r="122" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B122" s="25">
+        <v>9</v>
+      </c>
+      <c r="C122" s="25">
+        <v>22</v>
+      </c>
+      <c r="D122" s="25">
+        <v>2</v>
+      </c>
+      <c r="E122" s="45"/>
+      <c r="F122" s="45"/>
+      <c r="G122" s="45"/>
+      <c r="H122" s="45"/>
+      <c r="I122" s="45"/>
+      <c r="J122" s="45"/>
+      <c r="K122" s="45"/>
+      <c r="L122" s="45"/>
+      <c r="M122" s="45"/>
+      <c r="N122" s="45"/>
+    </row>
+    <row r="123" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B123" s="25">
+        <v>9</v>
+      </c>
+      <c r="C123" s="25">
+        <v>32</v>
+      </c>
+      <c r="D123" s="25">
+        <v>1</v>
+      </c>
+      <c r="E123" s="45"/>
+      <c r="F123" s="45"/>
+      <c r="G123" s="45"/>
+      <c r="H123" s="45"/>
+      <c r="I123" s="45"/>
+      <c r="J123" s="45"/>
+      <c r="K123" s="45"/>
+      <c r="L123" s="45"/>
+      <c r="M123" s="45"/>
+      <c r="N123" s="45"/>
+    </row>
+    <row r="124" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B124" s="25">
+        <v>10</v>
+      </c>
+      <c r="C124" s="25">
+        <v>18</v>
+      </c>
+      <c r="D124" s="25">
+        <v>2</v>
+      </c>
+      <c r="E124" s="45"/>
+      <c r="F124" s="45"/>
+      <c r="G124" s="45"/>
+      <c r="H124" s="45"/>
+      <c r="I124" s="45"/>
+      <c r="J124" s="45"/>
+      <c r="K124" s="45"/>
+      <c r="L124" s="45"/>
+      <c r="M124" s="45"/>
+      <c r="N124" s="45"/>
+    </row>
+    <row r="125" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B125" s="25">
+        <v>10</v>
+      </c>
+      <c r="C125" s="25">
+        <v>29</v>
+      </c>
+      <c r="D125" s="25">
+        <v>4</v>
+      </c>
+      <c r="E125" s="45"/>
+      <c r="F125" s="45"/>
+      <c r="G125" s="45"/>
+      <c r="H125" s="45"/>
+      <c r="I125" s="45"/>
+      <c r="J125" s="45"/>
+      <c r="K125" s="45"/>
+      <c r="L125" s="45"/>
+      <c r="M125" s="45"/>
+      <c r="N125" s="45"/>
+    </row>
+    <row r="126" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B126" s="25">
+        <v>11</v>
+      </c>
+      <c r="C126" s="25">
+        <v>33</v>
+      </c>
+      <c r="D126" s="25">
+        <v>2</v>
+      </c>
+      <c r="E126" s="45"/>
+      <c r="F126" s="45"/>
+      <c r="G126" s="45"/>
+      <c r="H126" s="45"/>
+      <c r="I126" s="45"/>
+      <c r="J126" s="45"/>
+      <c r="K126" s="45"/>
+      <c r="L126" s="45"/>
+      <c r="M126" s="45"/>
+      <c r="N126" s="45"/>
+    </row>
+    <row r="127" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B127" s="25">
+        <v>11</v>
+      </c>
+      <c r="C127" s="25">
+        <v>65</v>
+      </c>
+      <c r="D127" s="25">
+        <v>1</v>
+      </c>
+      <c r="E127" s="45"/>
+      <c r="F127" s="45"/>
+      <c r="G127" s="45"/>
+      <c r="H127" s="45"/>
+      <c r="I127" s="45"/>
+      <c r="J127" s="45"/>
+      <c r="K127" s="45"/>
+      <c r="L127" s="45"/>
+      <c r="M127" s="45"/>
+      <c r="N127" s="45"/>
+    </row>
+    <row r="128" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B128" s="25">
+        <v>11</v>
+      </c>
+      <c r="C128" s="25">
+        <v>1</v>
+      </c>
+      <c r="D128" s="25">
+        <v>1</v>
+      </c>
+      <c r="E128" s="45"/>
+      <c r="F128" s="45"/>
+      <c r="G128" s="45"/>
+      <c r="H128" s="45"/>
+      <c r="I128" s="45"/>
+      <c r="J128" s="45"/>
+      <c r="K128" s="45"/>
+      <c r="L128" s="45"/>
+      <c r="M128" s="45"/>
+      <c r="N128" s="45"/>
+    </row>
+    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B129" s="25">
+        <v>11</v>
+      </c>
+      <c r="C129" s="25">
+        <v>2</v>
+      </c>
+      <c r="D129" s="25">
+        <v>2</v>
+      </c>
+      <c r="E129" s="45"/>
+      <c r="F129" s="45"/>
+      <c r="G129" s="45"/>
+      <c r="H129" s="45"/>
+      <c r="I129" s="45"/>
+      <c r="J129" s="45"/>
+      <c r="K129" s="45"/>
+      <c r="L129" s="45"/>
+      <c r="M129" s="45"/>
+      <c r="N129" s="45"/>
+    </row>
+    <row r="130" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B130" s="25">
+        <v>11</v>
+      </c>
+      <c r="C130" s="25">
+        <v>5</v>
+      </c>
+      <c r="D130" s="25">
+        <v>5</v>
+      </c>
+      <c r="E130" s="45"/>
+      <c r="F130" s="45"/>
+      <c r="G130" s="45"/>
+      <c r="H130" s="45"/>
+      <c r="I130" s="45"/>
+      <c r="J130" s="45"/>
+      <c r="K130" s="45"/>
+      <c r="L130" s="45"/>
+      <c r="M130" s="45"/>
+      <c r="N130" s="45"/>
+    </row>
+    <row r="131" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B131" s="25">
+        <v>11</v>
+      </c>
+      <c r="C131" s="25">
+        <v>7</v>
+      </c>
+      <c r="D131" s="25">
+        <v>10</v>
+      </c>
+      <c r="E131" s="45"/>
+      <c r="F131" s="45"/>
+      <c r="G131" s="45"/>
+      <c r="H131" s="45"/>
+      <c r="I131" s="45"/>
+      <c r="J131" s="45"/>
+      <c r="K131" s="45"/>
+      <c r="L131" s="45"/>
+      <c r="M131" s="45"/>
+      <c r="N131" s="45"/>
+    </row>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B132" s="25">
+        <v>12</v>
+      </c>
+      <c r="C132" s="25">
+        <v>55</v>
+      </c>
+      <c r="D132" s="25">
+        <v>1</v>
+      </c>
+      <c r="E132" s="45"/>
+      <c r="F132" s="45"/>
+      <c r="G132" s="45"/>
+      <c r="H132" s="45"/>
+      <c r="I132" s="45"/>
+      <c r="J132" s="45"/>
+      <c r="K132" s="45"/>
+      <c r="L132" s="45"/>
+      <c r="M132" s="45"/>
+      <c r="N132" s="45"/>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B133" s="25">
+        <v>13</v>
+      </c>
+      <c r="C133" s="25">
+        <v>92</v>
+      </c>
+      <c r="D133" s="25">
+        <v>1</v>
+      </c>
+      <c r="E133" s="45"/>
+      <c r="F133" s="45"/>
+      <c r="G133" s="45"/>
+      <c r="H133" s="45"/>
+      <c r="I133" s="45"/>
+      <c r="J133" s="45"/>
+      <c r="K133" s="45"/>
+      <c r="L133" s="45"/>
+      <c r="M133" s="45"/>
+      <c r="N133" s="45"/>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B134" s="25">
+        <v>13</v>
+      </c>
+      <c r="C134" s="25">
+        <v>14</v>
+      </c>
+      <c r="D134" s="25">
+        <v>2</v>
+      </c>
+      <c r="E134" s="45"/>
+      <c r="F134" s="45"/>
+      <c r="G134" s="45"/>
+      <c r="H134" s="45"/>
+      <c r="I134" s="45"/>
+      <c r="J134" s="45"/>
+      <c r="K134" s="45"/>
+      <c r="L134" s="45"/>
+      <c r="M134" s="45"/>
+      <c r="N134" s="45"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B135" s="45"/>
+      <c r="C135" s="45"/>
+      <c r="D135" s="45"/>
+      <c r="E135" s="45"/>
+      <c r="F135" s="45"/>
+      <c r="G135" s="45"/>
+      <c r="H135" s="45"/>
+      <c r="I135" s="45"/>
+      <c r="J135" s="45"/>
+      <c r="K135" s="45"/>
+      <c r="L135" s="45"/>
+      <c r="M135" s="45"/>
+      <c r="N135" s="45"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="C73:E74"/>
+    <mergeCell ref="C79:D80"/>
+    <mergeCell ref="C86:F89"/>
+    <mergeCell ref="B93:C95"/>
+    <mergeCell ref="B99:D101"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>